--- a/src/test/resources/data/PPD/testData.xlsx
+++ b/src/test/resources/data/PPD/testData.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wsib-my.sharepoint.com/personal/kiran_kangula_wsib_on_ca/Documents/Documents/Automation/DigitalClaims/src/test/resources/data/BAT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wsib-my.sharepoint.com/personal/kiran_kangula_wsib_on_ca/Documents/Documents/Automation/DigitalClaims/src/test/resources/data/PPD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="13_ncr:1_{A3C00A53-B60F-4FFA-AC45-FA356BAFF82F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F70A9BF2-541A-485A-B2D7-8FE6B4BBD080}"/>
+  <xr:revisionPtr revIDLastSave="164" documentId="13_ncr:1_{A3C00A53-B60F-4FFA-AC45-FA356BAFF82F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C6BFF07-20B3-4194-BA25-1D5915810661}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GWCC" sheetId="1" r:id="rId1"/>
@@ -19,10 +19,12 @@
     <sheet name="eForm6_Mental" sheetId="4" r:id="rId4"/>
     <sheet name="eForm6_Construction" sheetId="5" r:id="rId5"/>
     <sheet name="eForm6_Other" sheetId="6" r:id="rId6"/>
+    <sheet name="WT" sheetId="7" r:id="rId7"/>
+    <sheet name="CAA" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4239" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="237">
   <si>
     <t>ReferenceNumber</t>
   </si>
@@ -514,18 +516,6 @@
     <t>Other industry</t>
   </si>
   <si>
-    <t>85128981</t>
-  </si>
-  <si>
-    <t>85128982</t>
-  </si>
-  <si>
-    <t>85128983</t>
-  </si>
-  <si>
-    <t>85128984</t>
-  </si>
-  <si>
     <t>Claim Number</t>
   </si>
   <si>
@@ -538,165 +528,9 @@
     <t/>
   </si>
   <si>
-    <t>32650628</t>
-  </si>
-  <si>
     <t>01/Jan/2000</t>
   </si>
   <si>
-    <t>922901</t>
-  </si>
-  <si>
-    <t>85129087</t>
-  </si>
-  <si>
-    <t>32650632</t>
-  </si>
-  <si>
-    <t>569669</t>
-  </si>
-  <si>
-    <t>85129134</t>
-  </si>
-  <si>
-    <t>32650680</t>
-  </si>
-  <si>
-    <t>570172</t>
-  </si>
-  <si>
-    <t>85129135</t>
-  </si>
-  <si>
-    <t>32650682</t>
-  </si>
-  <si>
-    <t>747161</t>
-  </si>
-  <si>
-    <t>85129136</t>
-  </si>
-  <si>
-    <t>32650684</t>
-  </si>
-  <si>
-    <t>921244</t>
-  </si>
-  <si>
-    <t>85129137</t>
-  </si>
-  <si>
-    <t>32650686</t>
-  </si>
-  <si>
-    <t>072432</t>
-  </si>
-  <si>
-    <t>85129138</t>
-  </si>
-  <si>
-    <t>85129139</t>
-  </si>
-  <si>
-    <t>85129169</t>
-  </si>
-  <si>
-    <t>32650716</t>
-  </si>
-  <si>
-    <t>131505</t>
-  </si>
-  <si>
-    <t>85129170</t>
-  </si>
-  <si>
-    <t>32650718</t>
-  </si>
-  <si>
-    <t>294890</t>
-  </si>
-  <si>
-    <t>85129171</t>
-  </si>
-  <si>
-    <t>32650720</t>
-  </si>
-  <si>
-    <t>392797</t>
-  </si>
-  <si>
-    <t>85129172</t>
-  </si>
-  <si>
-    <t>32650722</t>
-  </si>
-  <si>
-    <t>578609</t>
-  </si>
-  <si>
-    <t>85129173</t>
-  </si>
-  <si>
-    <t>32650724</t>
-  </si>
-  <si>
-    <t>365781</t>
-  </si>
-  <si>
-    <t>85129174</t>
-  </si>
-  <si>
-    <t>85129175</t>
-  </si>
-  <si>
-    <t>85129176</t>
-  </si>
-  <si>
-    <t>85129177</t>
-  </si>
-  <si>
-    <t>85129178</t>
-  </si>
-  <si>
-    <t>85129179</t>
-  </si>
-  <si>
-    <t>85129180</t>
-  </si>
-  <si>
-    <t>85129181</t>
-  </si>
-  <si>
-    <t>85129182</t>
-  </si>
-  <si>
-    <t>32650726</t>
-  </si>
-  <si>
-    <t>701980</t>
-  </si>
-  <si>
-    <t>85129183</t>
-  </si>
-  <si>
-    <t>85129184</t>
-  </si>
-  <si>
-    <t>32650728</t>
-  </si>
-  <si>
-    <t>932767</t>
-  </si>
-  <si>
-    <t>85129185</t>
-  </si>
-  <si>
-    <t>32650730</t>
-  </si>
-  <si>
-    <t>050344</t>
-  </si>
-  <si>
     <t>85129186</t>
   </si>
   <si>
@@ -706,30 +540,6 @@
     <t>153486</t>
   </si>
   <si>
-    <t>85129187</t>
-  </si>
-  <si>
-    <t>32650734</t>
-  </si>
-  <si>
-    <t>255589</t>
-  </si>
-  <si>
-    <t>85129188</t>
-  </si>
-  <si>
-    <t>32650736</t>
-  </si>
-  <si>
-    <t>330156</t>
-  </si>
-  <si>
-    <t>85129189</t>
-  </si>
-  <si>
-    <t>85129190</t>
-  </si>
-  <si>
     <t>32650738</t>
   </si>
   <si>
@@ -745,12 +555,6 @@
     <t>968191</t>
   </si>
   <si>
-    <t>85129192</t>
-  </si>
-  <si>
-    <t>85129339</t>
-  </si>
-  <si>
     <t>85129340</t>
   </si>
   <si>
@@ -770,14 +574,193 @@
   </si>
   <si>
     <t>85129343</t>
+  </si>
+  <si>
+    <t>claimnumber</t>
+  </si>
+  <si>
+    <t>lastname</t>
+  </si>
+  <si>
+    <t>dateofbirth</t>
+  </si>
+  <si>
+    <t>Author</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>expenseType</t>
+  </si>
+  <si>
+    <t>Repeated Travel</t>
+  </si>
+  <si>
+    <t>32710725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULNMVFQ </t>
+  </si>
+  <si>
+    <t>01/01/2000</t>
+  </si>
+  <si>
+    <t>Reason</t>
+  </si>
+  <si>
+    <t>Expenses</t>
+  </si>
+  <si>
+    <t>TotalKM</t>
+  </si>
+  <si>
+    <t>PubTransit</t>
+  </si>
+  <si>
+    <t>Parking</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>Meeting</t>
+  </si>
+  <si>
+    <t>Kilometers</t>
+  </si>
+  <si>
+    <t>1000</t>
+  </si>
+  <si>
+    <t>AdditionalInfo</t>
+  </si>
+  <si>
+    <t>Additiona information entered</t>
+  </si>
+  <si>
+    <t>OtherExpenseType</t>
+  </si>
+  <si>
+    <t>OtherExpenseDescription</t>
+  </si>
+  <si>
+    <t>OtherExpenseAmount</t>
+  </si>
+  <si>
+    <t>OtherAdditionalInfo</t>
+  </si>
+  <si>
+    <t>Textbooks</t>
+  </si>
+  <si>
+    <t>Description test</t>
+  </si>
+  <si>
+    <t>3000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other information </t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>Kiran_Kangula@wsib.on.ca</t>
+  </si>
+  <si>
+    <t>WT</t>
+  </si>
+  <si>
+    <t>Worker Travel</t>
+  </si>
+  <si>
+    <t>phonenumber</t>
+  </si>
+  <si>
+    <t>6470009998</t>
+  </si>
+  <si>
+    <t>ppdNel</t>
+  </si>
+  <si>
+    <t>receivedCa</t>
+  </si>
+  <si>
+    <t>otherClaimNumber</t>
+  </si>
+  <si>
+    <t>isEmployed</t>
+  </si>
+  <si>
+    <t>usesDeviceAtWork</t>
+  </si>
+  <si>
+    <t>employerPaysForUniform</t>
+  </si>
+  <si>
+    <t>uniformOverClothing</t>
+  </si>
+  <si>
+    <t>damage</t>
+  </si>
+  <si>
+    <t>startDate</t>
+  </si>
+  <si>
+    <t>hoursPerDay</t>
+  </si>
+  <si>
+    <t>daysPerWeek</t>
+  </si>
+  <si>
+    <t>UpperBody</t>
+  </si>
+  <si>
+    <t>LowerBody</t>
+  </si>
+  <si>
+    <t>OtherDevice</t>
+  </si>
+  <si>
+    <t>metalParts</t>
+  </si>
+  <si>
+    <t>repairOrReplaced</t>
+  </si>
+  <si>
+    <t>45609098</t>
+  </si>
+  <si>
+    <t>Over</t>
+  </si>
+  <si>
+    <t>Test Damage</t>
+  </si>
+  <si>
+    <t>01/01/2024</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Arm Brace</t>
+  </si>
+  <si>
+    <t>Leg Prothesis</t>
+  </si>
+  <si>
+    <t>Clothing</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -789,6 +772,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -811,15 +802,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="17">
@@ -1272,20 +1266,20 @@
   <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="16.42578125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="11.5703125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -1301,76 +1295,76 @@
   <dimension ref="A1:BY2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="2" max="2" customWidth="true" width="16.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="11.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="7.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="14.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="13.85546875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="13.42578125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="20.42578125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="10.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="9.7109375"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="9.42578125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="7.5703125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="14.7109375"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="10.85546875"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="14.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="22.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="8.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="18.5703125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="16.42578125"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" width="19.7109375"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="19.85546875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="19.42578125"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="23.85546875"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" width="12.85546875"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" width="19.5703125"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" width="15.140625"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" width="13.7109375"/>
-    <col min="38" max="38" bestFit="true" customWidth="true" width="16.42578125"/>
-    <col min="39" max="39" bestFit="true" customWidth="true" width="14.42578125"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" width="13.42578125"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" width="16.140625"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" width="17.28515625"/>
-    <col min="45" max="45" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" width="21.7109375"/>
-    <col min="47" max="47" bestFit="true" customWidth="true" width="12.28515625"/>
-    <col min="48" max="48" bestFit="true" customWidth="true" width="13.85546875"/>
-    <col min="49" max="49" bestFit="true" customWidth="true" width="21.42578125"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" width="17.28515625"/>
-    <col min="51" max="51" bestFit="true" customWidth="true" width="25.28515625"/>
-    <col min="52" max="54" customWidth="true" width="28.0"/>
-    <col min="55" max="55" bestFit="true" customWidth="true" width="23.5703125"/>
-    <col min="56" max="56" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="57" max="57" bestFit="true" customWidth="true" width="42.140625"/>
-    <col min="58" max="59" customWidth="true" width="33.85546875"/>
-    <col min="60" max="60" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="61" max="61" bestFit="true" customWidth="true" width="21.7109375"/>
-    <col min="62" max="62" customWidth="true" width="33.85546875"/>
-    <col min="63" max="63" bestFit="true" customWidth="true" width="10.140625"/>
-    <col min="64" max="64" customWidth="true" width="25.140625"/>
-    <col min="65" max="65" customWidth="true" width="14.7109375"/>
-    <col min="66" max="66" customWidth="true" width="20.0"/>
-    <col min="67" max="67" customWidth="true" width="33.85546875"/>
-    <col min="68" max="68" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="69" max="69" customWidth="true" width="33.85546875"/>
-    <col min="70" max="71" customWidth="true" width="23.0"/>
-    <col min="72" max="72" customWidth="true" width="18.42578125"/>
-    <col min="73" max="73" bestFit="true" customWidth="true" width="36.85546875"/>
-    <col min="74" max="75" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="76" max="78" customWidth="true" width="33.85546875"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="9" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="52" max="54" width="28" customWidth="1"/>
+    <col min="55" max="55" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="58" max="59" width="33.85546875" customWidth="1"/>
+    <col min="60" max="60" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="33.85546875" customWidth="1"/>
+    <col min="63" max="63" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="25.140625" customWidth="1"/>
+    <col min="65" max="65" width="14.7109375" customWidth="1"/>
+    <col min="66" max="66" width="20" customWidth="1"/>
+    <col min="67" max="67" width="33.85546875" customWidth="1"/>
+    <col min="68" max="68" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="33.85546875" customWidth="1"/>
+    <col min="70" max="71" width="23" customWidth="1"/>
+    <col min="72" max="72" width="18.42578125" customWidth="1"/>
+    <col min="73" max="73" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="74" max="75" width="19" bestFit="1" customWidth="1"/>
+    <col min="76" max="78" width="33.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:77" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1378,13 +1372,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
@@ -1608,75 +1602,75 @@
     </row>
     <row r="2" spans="1:77" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>237</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>166</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>238</v>
-      </c>
-      <c r="E2" t="s" s="0">
+        <v>170</v>
+      </c>
+      <c r="B2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s" s="0">
+      <c r="F2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s" s="0">
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" t="s" s="0">
-        <v>164</v>
-      </c>
-      <c r="J2" t="s" s="0">
+      <c r="I2" t="s">
+        <v>160</v>
+      </c>
+      <c r="J2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" t="s" s="0">
+      <c r="K2" t="s">
         <v>20</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M2" t="s" s="0">
+      <c r="M2" t="s">
         <v>22</v>
       </c>
-      <c r="N2" t="s" s="0">
+      <c r="N2" t="s">
         <v>23</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="P2" t="s" s="0">
+      <c r="P2" t="s">
         <v>26</v>
       </c>
-      <c r="Q2" t="s" s="0">
-        <v>164</v>
-      </c>
-      <c r="R2" t="s" s="0">
+      <c r="Q2" t="s">
+        <v>160</v>
+      </c>
+      <c r="R2" t="s">
         <v>80</v>
       </c>
-      <c r="S2" t="s" s="0">
+      <c r="S2" t="s">
         <v>27</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="U2" t="s" s="0">
+      <c r="U2" t="s">
         <v>80</v>
       </c>
-      <c r="V2" t="s" s="0">
+      <c r="V2" t="s">
         <v>43</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="X2" t="s" s="0">
+      <c r="X2" t="s">
         <v>25</v>
       </c>
       <c r="Y2" s="1" t="s">
@@ -1688,31 +1682,31 @@
       <c r="AA2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>46</v>
       </c>
-      <c r="AC2" t="s" s="0">
+      <c r="AC2" t="s">
         <v>47</v>
       </c>
       <c r="AD2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AE2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AF2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AG2" t="s" s="0">
+      <c r="AE2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG2" t="s">
         <v>49</v>
       </c>
-      <c r="AH2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AI2" t="s" s="0">
+      <c r="AH2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AI2" t="s">
         <v>52</v>
       </c>
-      <c r="AJ2" t="s" s="0">
+      <c r="AJ2" t="s">
         <v>57</v>
       </c>
       <c r="AK2" s="1" t="s">
@@ -1724,118 +1718,118 @@
       <c r="AM2" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AN2" t="s" s="0">
+      <c r="AN2" t="s">
         <v>59</v>
       </c>
-      <c r="AO2" t="s" s="0">
+      <c r="AO2" t="s">
         <v>60</v>
       </c>
-      <c r="AP2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AQ2" t="s" s="0">
+      <c r="AP2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ2" t="s">
         <v>66</v>
       </c>
-      <c r="AR2" t="s" s="0">
+      <c r="AR2" t="s">
         <v>67</v>
       </c>
-      <c r="AS2" t="s" s="0">
+      <c r="AS2" t="s">
         <v>68</v>
       </c>
       <c r="AT2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AU2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AV2" t="s" s="0">
+      <c r="AU2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV2" t="s">
         <v>17</v>
       </c>
       <c r="AW2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AX2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AY2" t="s" s="0">
+      <c r="AX2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AY2" t="s">
         <v>76</v>
       </c>
-      <c r="AZ2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BA2" t="s" s="0">
+      <c r="AZ2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BA2" t="s">
         <v>90</v>
       </c>
-      <c r="BB2" t="s" s="0">
+      <c r="BB2" t="s">
         <v>91</v>
       </c>
-      <c r="BC2" t="s" s="0">
+      <c r="BC2" t="s">
         <v>83</v>
       </c>
-      <c r="BD2" t="s" s="0">
+      <c r="BD2" t="s">
         <v>83</v>
       </c>
-      <c r="BE2" t="s" s="0">
+      <c r="BE2" t="s">
         <v>85</v>
       </c>
-      <c r="BF2" t="s" s="0">
+      <c r="BF2" t="s">
         <v>87</v>
       </c>
-      <c r="BG2" t="s" s="0">
+      <c r="BG2" t="s">
         <v>89</v>
       </c>
-      <c r="BH2" t="s" s="0">
+      <c r="BH2" t="s">
         <v>80</v>
       </c>
-      <c r="BI2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BJ2" t="s" s="0">
+      <c r="BI2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BJ2" t="s">
         <v>83</v>
       </c>
-      <c r="BK2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BL2" t="s" s="0">
+      <c r="BK2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BL2" t="s">
         <v>83</v>
       </c>
-      <c r="BM2" t="s" s="0">
+      <c r="BM2" t="s">
         <v>99</v>
       </c>
-      <c r="BN2" t="s" s="0">
+      <c r="BN2" t="s">
         <v>100</v>
       </c>
-      <c r="BO2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BP2" t="s" s="0">
+      <c r="BO2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BP2" t="s">
         <v>83</v>
       </c>
-      <c r="BQ2" t="s" s="0">
+      <c r="BQ2" t="s">
         <v>105</v>
       </c>
-      <c r="BR2" t="s" s="0">
+      <c r="BR2" t="s">
         <v>106</v>
       </c>
-      <c r="BS2" t="s" s="0">
+      <c r="BS2" t="s">
         <v>108</v>
       </c>
-      <c r="BT2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BU2" t="s" s="0">
+      <c r="BT2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BU2" t="s">
         <v>110</v>
       </c>
-      <c r="BV2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BW2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BX2" t="s" s="0">
+      <c r="BV2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BX2" t="s">
         <v>114</v>
       </c>
-      <c r="BY2" t="s" s="0">
+      <c r="BY2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1862,74 +1856,74 @@
   <dimension ref="A1:BW2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="13.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="4.140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="14.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="33.85546875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="13.42578125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="20.42578125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="10.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="9.7109375"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="9.42578125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="7.5703125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="14.7109375"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="10.85546875"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="14.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="22.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="8.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="18.5703125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="16.42578125"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" width="19.7109375"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="19.85546875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="19.42578125"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="23.85546875"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" width="12.85546875"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" width="19.5703125"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" width="15.140625"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" width="19.85546875"/>
-    <col min="38" max="38" customWidth="true" width="19.85546875"/>
-    <col min="39" max="39" bestFit="true" customWidth="true" width="15.140625"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" width="16.140625"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" width="17.28515625"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" width="21.7109375"/>
-    <col min="45" max="45" bestFit="true" customWidth="true" width="12.28515625"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" width="13.85546875"/>
-    <col min="47" max="47" bestFit="true" customWidth="true" width="21.42578125"/>
-    <col min="48" max="48" bestFit="true" customWidth="true" width="17.28515625"/>
-    <col min="49" max="49" bestFit="true" customWidth="true" width="25.28515625"/>
-    <col min="50" max="52" customWidth="true" width="28.0"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="23.5703125"/>
-    <col min="54" max="54" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="55" max="55" bestFit="true" customWidth="true" width="42.140625"/>
-    <col min="56" max="57" customWidth="true" width="33.85546875"/>
-    <col min="58" max="58" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="59" max="59" bestFit="true" customWidth="true" width="21.7109375"/>
-    <col min="60" max="60" customWidth="true" width="33.85546875"/>
-    <col min="61" max="61" bestFit="true" customWidth="true" width="10.140625"/>
-    <col min="62" max="62" customWidth="true" width="25.140625"/>
-    <col min="63" max="63" customWidth="true" width="14.7109375"/>
-    <col min="64" max="64" customWidth="true" width="20.0"/>
-    <col min="65" max="65" customWidth="true" width="33.85546875"/>
-    <col min="66" max="66" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="67" max="67" customWidth="true" width="33.85546875"/>
-    <col min="68" max="69" customWidth="true" width="23.0"/>
-    <col min="70" max="70" customWidth="true" width="18.42578125"/>
-    <col min="71" max="71" bestFit="true" customWidth="true" width="36.85546875"/>
-    <col min="72" max="73" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="74" max="76" customWidth="true" width="33.85546875"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="19.85546875" customWidth="1"/>
+    <col min="39" max="39" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="50" max="52" width="28" customWidth="1"/>
+    <col min="53" max="53" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="56" max="57" width="33.85546875" customWidth="1"/>
+    <col min="58" max="58" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="33.85546875" customWidth="1"/>
+    <col min="61" max="61" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="25.140625" customWidth="1"/>
+    <col min="63" max="63" width="14.7109375" customWidth="1"/>
+    <col min="64" max="64" width="20" customWidth="1"/>
+    <col min="65" max="65" width="33.85546875" customWidth="1"/>
+    <col min="66" max="66" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="33.85546875" customWidth="1"/>
+    <col min="68" max="69" width="23" customWidth="1"/>
+    <col min="70" max="70" width="18.42578125" customWidth="1"/>
+    <col min="71" max="71" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="72" max="73" width="19" bestFit="1" customWidth="1"/>
+    <col min="74" max="76" width="33.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:75" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1937,13 +1931,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
@@ -2160,76 +2154,76 @@
       </c>
     </row>
     <row r="2" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="0">
-        <v>218</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>219</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>166</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>220</v>
-      </c>
-      <c r="E2" t="s" s="0">
+      <c r="A2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s" s="0">
+      <c r="F2" t="s">
         <v>119</v>
       </c>
-      <c r="G2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s" s="0">
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" t="s" s="0">
-        <v>164</v>
-      </c>
-      <c r="J2" t="s" s="0">
+      <c r="I2" t="s">
+        <v>160</v>
+      </c>
+      <c r="J2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" t="s" s="0">
+      <c r="K2" t="s">
         <v>20</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M2" t="s" s="0">
+      <c r="M2" t="s">
         <v>22</v>
       </c>
-      <c r="N2" t="s" s="0">
+      <c r="N2" t="s">
         <v>23</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="P2" t="s" s="0">
+      <c r="P2" t="s">
         <v>26</v>
       </c>
-      <c r="Q2" t="s" s="0">
-        <v>164</v>
-      </c>
-      <c r="R2" t="s" s="0">
+      <c r="Q2" t="s">
+        <v>160</v>
+      </c>
+      <c r="R2" t="s">
         <v>80</v>
       </c>
-      <c r="S2" t="s" s="0">
+      <c r="S2" t="s">
         <v>27</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="U2" t="s" s="0">
+      <c r="U2" t="s">
         <v>80</v>
       </c>
-      <c r="V2" t="s" s="0">
+      <c r="V2" t="s">
         <v>43</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="X2" t="s" s="0">
+      <c r="X2" t="s">
         <v>25</v>
       </c>
       <c r="Y2" s="1" t="s">
@@ -2241,148 +2235,148 @@
       <c r="AA2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>46</v>
       </c>
-      <c r="AC2" t="s" s="0">
+      <c r="AC2" t="s">
         <v>47</v>
       </c>
       <c r="AD2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AE2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AF2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AG2" t="s" s="0">
+      <c r="AE2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG2" t="s">
         <v>49</v>
       </c>
-      <c r="AH2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AI2" t="s" s="0">
+      <c r="AH2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AI2" t="s">
         <v>52</v>
       </c>
-      <c r="AJ2" t="s" s="0">
+      <c r="AJ2" t="s">
         <v>57</v>
       </c>
-      <c r="AK2" t="s" s="0">
+      <c r="AK2" t="s">
         <v>123</v>
       </c>
-      <c r="AL2" t="s" s="0">
+      <c r="AL2" t="s">
         <v>124</v>
       </c>
       <c r="AM2" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AN2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AO2" t="s" s="0">
+      <c r="AN2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO2" t="s">
         <v>66</v>
       </c>
-      <c r="AP2" t="s" s="0">
+      <c r="AP2" t="s">
         <v>67</v>
       </c>
-      <c r="AQ2" t="s" s="0">
+      <c r="AQ2" t="s">
         <v>68</v>
       </c>
       <c r="AR2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AS2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AT2" t="s" s="0">
+      <c r="AS2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AT2" t="s">
         <v>17</v>
       </c>
       <c r="AU2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AV2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AW2" t="s" s="0">
+      <c r="AV2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AW2" t="s">
         <v>76</v>
       </c>
-      <c r="AX2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AY2" t="s" s="0">
+      <c r="AX2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AY2" t="s">
         <v>90</v>
       </c>
-      <c r="AZ2" t="s" s="0">
+      <c r="AZ2" t="s">
         <v>91</v>
       </c>
-      <c r="BA2" t="s" s="0">
+      <c r="BA2" t="s">
         <v>83</v>
       </c>
-      <c r="BB2" t="s" s="0">
+      <c r="BB2" t="s">
         <v>83</v>
       </c>
-      <c r="BC2" t="s" s="0">
+      <c r="BC2" t="s">
         <v>85</v>
       </c>
-      <c r="BD2" t="s" s="0">
+      <c r="BD2" t="s">
         <v>87</v>
       </c>
-      <c r="BE2" t="s" s="0">
+      <c r="BE2" t="s">
         <v>89</v>
       </c>
-      <c r="BF2" t="s" s="0">
+      <c r="BF2" t="s">
         <v>80</v>
       </c>
-      <c r="BG2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BH2" t="s" s="0">
+      <c r="BG2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BH2" t="s">
         <v>83</v>
       </c>
-      <c r="BI2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BJ2" t="s" s="0">
+      <c r="BI2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BJ2" t="s">
         <v>83</v>
       </c>
-      <c r="BK2" t="s" s="0">
+      <c r="BK2" t="s">
         <v>99</v>
       </c>
-      <c r="BL2" t="s" s="0">
+      <c r="BL2" t="s">
         <v>100</v>
       </c>
-      <c r="BM2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BN2" t="s" s="0">
+      <c r="BM2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BN2" t="s">
         <v>83</v>
       </c>
-      <c r="BO2" t="s" s="0">
+      <c r="BO2" t="s">
         <v>105</v>
       </c>
-      <c r="BP2" t="s" s="0">
+      <c r="BP2" t="s">
         <v>106</v>
       </c>
-      <c r="BQ2" t="s" s="0">
+      <c r="BQ2" t="s">
         <v>108</v>
       </c>
-      <c r="BR2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BS2" t="s" s="0">
+      <c r="BR2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BS2" t="s">
         <v>110</v>
       </c>
-      <c r="BT2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BU2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BV2" t="s" s="0">
+      <c r="BT2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BV2" t="s">
         <v>114</v>
       </c>
-      <c r="BW2" t="s" s="0">
+      <c r="BW2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2408,74 +2402,74 @@
   <dimension ref="A1:BX2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="13.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="4.140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="14.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="24.28515625"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="20.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="10.140625"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="9.7109375"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="9.42578125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="7.5703125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="14.7109375"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="10.85546875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="14.85546875"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="22.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="8.0"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="18.5703125"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="16.42578125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="19.7109375"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" width="19.85546875"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="19.42578125"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="23.85546875"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" width="19.5703125"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" width="17.28515625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" width="15.140625"/>
-    <col min="37" max="38" customWidth="true" width="15.140625"/>
-    <col min="39" max="39" bestFit="true" customWidth="true" width="13.42578125"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" width="16.140625"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" width="17.28515625"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="45" max="45" bestFit="true" customWidth="true" width="21.7109375"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" width="12.28515625"/>
-    <col min="47" max="47" bestFit="true" customWidth="true" width="13.85546875"/>
-    <col min="48" max="48" bestFit="true" customWidth="true" width="21.42578125"/>
-    <col min="49" max="49" bestFit="true" customWidth="true" width="17.28515625"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" width="25.28515625"/>
-    <col min="51" max="53" customWidth="true" width="28.0"/>
-    <col min="54" max="54" bestFit="true" customWidth="true" width="23.5703125"/>
-    <col min="55" max="55" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="56" max="56" bestFit="true" customWidth="true" width="42.140625"/>
-    <col min="57" max="58" customWidth="true" width="33.85546875"/>
-    <col min="59" max="59" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="60" max="60" bestFit="true" customWidth="true" width="21.7109375"/>
-    <col min="61" max="61" customWidth="true" width="33.85546875"/>
-    <col min="62" max="62" bestFit="true" customWidth="true" width="10.140625"/>
-    <col min="63" max="63" customWidth="true" width="25.140625"/>
-    <col min="64" max="64" customWidth="true" width="14.7109375"/>
-    <col min="65" max="65" customWidth="true" width="20.0"/>
-    <col min="66" max="66" customWidth="true" width="33.85546875"/>
-    <col min="67" max="67" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="68" max="68" customWidth="true" width="33.85546875"/>
-    <col min="69" max="70" customWidth="true" width="23.0"/>
-    <col min="71" max="71" customWidth="true" width="18.42578125"/>
-    <col min="72" max="72" bestFit="true" customWidth="true" width="36.85546875"/>
-    <col min="73" max="74" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="75" max="77" customWidth="true" width="33.85546875"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="15.140625" customWidth="1"/>
+    <col min="39" max="39" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="9" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="51" max="53" width="28" customWidth="1"/>
+    <col min="54" max="54" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="57" max="58" width="33.85546875" customWidth="1"/>
+    <col min="59" max="59" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="33.85546875" customWidth="1"/>
+    <col min="62" max="62" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="25.140625" customWidth="1"/>
+    <col min="64" max="64" width="14.7109375" customWidth="1"/>
+    <col min="65" max="65" width="20" customWidth="1"/>
+    <col min="66" max="66" width="33.85546875" customWidth="1"/>
+    <col min="67" max="67" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="33.85546875" customWidth="1"/>
+    <col min="69" max="70" width="23" customWidth="1"/>
+    <col min="71" max="71" width="18.42578125" customWidth="1"/>
+    <col min="72" max="72" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="73" max="74" width="19" bestFit="1" customWidth="1"/>
+    <col min="75" max="77" width="33.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:76" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2483,13 +2477,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
@@ -2709,73 +2703,73 @@
       </c>
     </row>
     <row r="2" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="0">
-        <v>239</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>240</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>166</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="E2" t="s" s="0">
+      <c r="A2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s" s="0">
+      <c r="F2" t="s">
         <v>126</v>
       </c>
-      <c r="G2" t="s" s="0">
+      <c r="G2" t="s">
         <v>127</v>
       </c>
-      <c r="H2" t="s" s="0">
-        <v>164</v>
-      </c>
-      <c r="I2" t="s" s="0">
+      <c r="H2" t="s">
+        <v>160</v>
+      </c>
+      <c r="I2" t="s">
         <v>19</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="J2" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>22</v>
       </c>
-      <c r="M2" t="s" s="0">
+      <c r="M2" t="s">
         <v>23</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="O2" t="s" s="0">
+      <c r="O2" t="s">
         <v>26</v>
       </c>
-      <c r="P2" t="s" s="0">
-        <v>164</v>
-      </c>
-      <c r="Q2" t="s" s="0">
+      <c r="P2" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q2" t="s">
         <v>80</v>
       </c>
-      <c r="R2" t="s" s="0">
+      <c r="R2" t="s">
         <v>27</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="T2" t="s" s="0">
+      <c r="T2" t="s">
         <v>80</v>
       </c>
-      <c r="U2" t="s" s="0">
+      <c r="U2" t="s">
         <v>43</v>
       </c>
       <c r="V2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="W2" t="s" s="0">
+      <c r="W2" t="s">
         <v>25</v>
       </c>
       <c r="X2" s="1" t="s">
@@ -2787,31 +2781,31 @@
       <c r="Z2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA2" t="s" s="0">
+      <c r="AA2" t="s">
         <v>46</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>47</v>
       </c>
       <c r="AC2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AD2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AE2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AF2" t="s" s="0">
+      <c r="AD2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF2" t="s">
         <v>49</v>
       </c>
-      <c r="AG2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AH2" t="s" s="0">
+      <c r="AG2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH2" t="s">
         <v>52</v>
       </c>
-      <c r="AI2" t="s" s="0">
+      <c r="AI2" t="s">
         <v>57</v>
       </c>
       <c r="AJ2" s="1" t="s">
@@ -2823,118 +2817,118 @@
       <c r="AL2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AM2" t="s" s="0">
+      <c r="AM2" t="s">
         <v>59</v>
       </c>
-      <c r="AN2" t="s" s="0">
+      <c r="AN2" t="s">
         <v>60</v>
       </c>
-      <c r="AO2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AP2" t="s" s="0">
+      <c r="AO2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP2" t="s">
         <v>66</v>
       </c>
-      <c r="AQ2" t="s" s="0">
+      <c r="AQ2" t="s">
         <v>67</v>
       </c>
-      <c r="AR2" t="s" s="0">
+      <c r="AR2" t="s">
         <v>68</v>
       </c>
       <c r="AS2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AT2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AU2" t="s" s="0">
+      <c r="AT2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU2" t="s">
         <v>17</v>
       </c>
       <c r="AV2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AW2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AX2" t="s" s="0">
+      <c r="AW2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AX2" t="s">
         <v>76</v>
       </c>
-      <c r="AY2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AZ2" t="s" s="0">
+      <c r="AY2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ2" t="s">
         <v>90</v>
       </c>
-      <c r="BA2" t="s" s="0">
+      <c r="BA2" t="s">
         <v>91</v>
       </c>
-      <c r="BB2" t="s" s="0">
+      <c r="BB2" t="s">
         <v>83</v>
       </c>
-      <c r="BC2" t="s" s="0">
+      <c r="BC2" t="s">
         <v>83</v>
       </c>
-      <c r="BD2" t="s" s="0">
+      <c r="BD2" t="s">
         <v>85</v>
       </c>
-      <c r="BE2" t="s" s="0">
+      <c r="BE2" t="s">
         <v>87</v>
       </c>
-      <c r="BF2" t="s" s="0">
+      <c r="BF2" t="s">
         <v>89</v>
       </c>
-      <c r="BG2" t="s" s="0">
+      <c r="BG2" t="s">
         <v>80</v>
       </c>
-      <c r="BH2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BI2" t="s" s="0">
+      <c r="BH2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BI2" t="s">
         <v>83</v>
       </c>
-      <c r="BJ2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BK2" t="s" s="0">
+      <c r="BJ2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BK2" t="s">
         <v>83</v>
       </c>
-      <c r="BL2" t="s" s="0">
+      <c r="BL2" t="s">
         <v>99</v>
       </c>
-      <c r="BM2" t="s" s="0">
+      <c r="BM2" t="s">
         <v>100</v>
       </c>
-      <c r="BN2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BO2" t="s" s="0">
+      <c r="BN2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BO2" t="s">
         <v>83</v>
       </c>
-      <c r="BP2" t="s" s="0">
+      <c r="BP2" t="s">
         <v>105</v>
       </c>
-      <c r="BQ2" t="s" s="0">
+      <c r="BQ2" t="s">
         <v>106</v>
       </c>
-      <c r="BR2" t="s" s="0">
+      <c r="BR2" t="s">
         <v>108</v>
       </c>
-      <c r="BS2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BT2" t="s" s="0">
+      <c r="BS2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BT2" t="s">
         <v>110</v>
       </c>
-      <c r="BU2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BV2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BW2" t="s" s="0">
+      <c r="BU2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BW2" t="s">
         <v>114</v>
       </c>
-      <c r="BX2" t="s" s="0">
+      <c r="BX2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2963,34 +2957,34 @@
   <dimension ref="A1:AH2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="13.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="4.140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="23.28515625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="10.140625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="9.7109375"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="9.42578125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="7.5703125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="14.7109375"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="14.85546875"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="22.85546875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="8.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="12.85546875"/>
-    <col min="22" max="23" customWidth="true" width="18.42578125"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="19.5703125"/>
-    <col min="27" max="29" customWidth="true" width="19.5703125"/>
-    <col min="30" max="32" customWidth="true" width="17.28515625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="19.85546875"/>
-    <col min="34" max="35" customWidth="true" width="33.85546875"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="18.42578125" customWidth="1"/>
+    <col min="24" max="24" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="19.5703125" customWidth="1"/>
+    <col min="30" max="32" width="17.28515625" customWidth="1"/>
+    <col min="33" max="33" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="33.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2998,13 +2992,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
@@ -3098,58 +3092,58 @@
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="0">
-        <v>242</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>229</v>
-      </c>
-      <c r="C2" t="s" s="0">
+      <c r="A2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D2" t="s">
         <v>166</v>
       </c>
-      <c r="D2" t="s" s="0">
-        <v>230</v>
-      </c>
-      <c r="E2" t="s" s="0">
+      <c r="E2" t="s">
         <v>133</v>
       </c>
-      <c r="F2" t="s" s="0">
+      <c r="F2" t="s">
         <v>141</v>
       </c>
-      <c r="G2" t="s" s="0">
+      <c r="G2" t="s">
         <v>134</v>
       </c>
-      <c r="H2" t="s" s="0">
+      <c r="H2" t="s">
         <v>19</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="I2" t="s">
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K2" t="s" s="0">
+      <c r="K2" t="s">
         <v>22</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>23</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="N2" t="s" s="0">
+      <c r="N2" t="s">
         <v>80</v>
       </c>
-      <c r="O2" t="s" s="0">
+      <c r="O2" t="s">
         <v>27</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" t="s" s="0">
+      <c r="Q2" t="s">
         <v>80</v>
       </c>
-      <c r="R2" t="s" s="0">
+      <c r="R2" t="s">
         <v>43</v>
       </c>
       <c r="S2" s="1" t="s">
@@ -3158,46 +3152,46 @@
       <c r="T2" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="U2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="V2" t="s" s="0">
+      <c r="U2" t="s">
+        <v>17</v>
+      </c>
+      <c r="V2" t="s">
         <v>141</v>
       </c>
-      <c r="W2" t="s" s="0">
+      <c r="W2" t="s">
         <v>141</v>
       </c>
-      <c r="X2" t="s" s="0">
+      <c r="X2" t="s">
         <v>49</v>
       </c>
-      <c r="Y2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="Z2" t="s" s="0">
+      <c r="Y2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z2" t="s">
         <v>52</v>
       </c>
-      <c r="AA2" t="s" s="0">
+      <c r="AA2" t="s">
         <v>143</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>83</v>
       </c>
-      <c r="AC2" t="s" s="0">
+      <c r="AC2" t="s">
         <v>145</v>
       </c>
-      <c r="AD2" t="s" s="0">
+      <c r="AD2" t="s">
         <v>43</v>
       </c>
-      <c r="AE2" t="s" s="0">
+      <c r="AE2" t="s">
         <v>148</v>
       </c>
-      <c r="AF2" t="s" s="0">
+      <c r="AF2" t="s">
         <v>150</v>
       </c>
-      <c r="AG2" t="s" s="0">
+      <c r="AG2" t="s">
         <v>43</v>
       </c>
-      <c r="AH2" t="s" s="0">
+      <c r="AH2" t="s">
         <v>114</v>
       </c>
     </row>
@@ -3218,34 +3212,34 @@
   <dimension ref="A1:AH2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="13.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="4.140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="23.28515625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="10.140625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="9.7109375"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="9.42578125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="7.5703125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="14.7109375"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="14.85546875"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="22.85546875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="8.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="12.85546875"/>
-    <col min="22" max="23" customWidth="true" width="18.42578125"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="19.5703125"/>
-    <col min="27" max="29" customWidth="true" width="19.5703125"/>
-    <col min="30" max="32" customWidth="true" width="17.28515625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="19.85546875"/>
-    <col min="34" max="35" customWidth="true" width="33.85546875"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="18.42578125" customWidth="1"/>
+    <col min="24" max="24" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="19.5703125" customWidth="1"/>
+    <col min="30" max="32" width="17.28515625" customWidth="1"/>
+    <col min="33" max="33" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="33.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3253,13 +3247,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
@@ -3353,58 +3347,58 @@
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="0">
-        <v>231</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>232</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>166</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>233</v>
-      </c>
-      <c r="E2" t="s" s="0">
+      <c r="A2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E2" t="s">
         <v>133</v>
       </c>
-      <c r="F2" t="s" s="0">
+      <c r="F2" t="s">
         <v>141</v>
       </c>
-      <c r="G2" t="s" s="0">
+      <c r="G2" t="s">
         <v>156</v>
       </c>
-      <c r="H2" t="s" s="0">
+      <c r="H2" t="s">
         <v>19</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="I2" t="s">
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K2" t="s" s="0">
+      <c r="K2" t="s">
         <v>22</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>23</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="N2" t="s" s="0">
+      <c r="N2" t="s">
         <v>80</v>
       </c>
-      <c r="O2" t="s" s="0">
+      <c r="O2" t="s">
         <v>27</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" t="s" s="0">
+      <c r="Q2" t="s">
         <v>80</v>
       </c>
-      <c r="R2" t="s" s="0">
+      <c r="R2" t="s">
         <v>43</v>
       </c>
       <c r="S2" s="1" t="s">
@@ -3413,46 +3407,46 @@
       <c r="T2" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="U2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="V2" t="s" s="0">
+      <c r="U2" t="s">
+        <v>17</v>
+      </c>
+      <c r="V2" t="s">
         <v>141</v>
       </c>
-      <c r="W2" t="s" s="0">
+      <c r="W2" t="s">
         <v>141</v>
       </c>
-      <c r="X2" t="s" s="0">
+      <c r="X2" t="s">
         <v>49</v>
       </c>
-      <c r="Y2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="Z2" t="s" s="0">
+      <c r="Y2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z2" t="s">
         <v>52</v>
       </c>
-      <c r="AA2" t="s" s="0">
+      <c r="AA2" t="s">
         <v>143</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>83</v>
       </c>
-      <c r="AC2" t="s" s="0">
+      <c r="AC2" t="s">
         <v>145</v>
       </c>
-      <c r="AD2" t="s" s="0">
+      <c r="AD2" t="s">
         <v>43</v>
       </c>
-      <c r="AE2" t="s" s="0">
+      <c r="AE2" t="s">
         <v>148</v>
       </c>
-      <c r="AF2" t="s" s="0">
+      <c r="AF2" t="s">
         <v>150</v>
       </c>
-      <c r="AG2" t="s" s="0">
+      <c r="AG2" t="s">
         <v>43</v>
       </c>
-      <c r="AH2" t="s" s="0">
+      <c r="AH2" t="s">
         <v>114</v>
       </c>
     </row>
@@ -3462,4 +3456,316 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0D9716D-5E3D-4891-AF91-0A6D708F5D9E}">
+  <dimension ref="A1:R2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="11.140625" customWidth="1"/>
+    <col min="11" max="11" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="18" width="12.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F1" t="s">
+        <v>188</v>
+      </c>
+      <c r="G1" t="s">
+        <v>189</v>
+      </c>
+      <c r="H1" t="s">
+        <v>190</v>
+      </c>
+      <c r="I1" t="s">
+        <v>191</v>
+      </c>
+      <c r="J1" t="s">
+        <v>192</v>
+      </c>
+      <c r="K1" t="s">
+        <v>196</v>
+      </c>
+      <c r="L1" t="s">
+        <v>198</v>
+      </c>
+      <c r="M1" t="s">
+        <v>199</v>
+      </c>
+      <c r="N1" t="s">
+        <v>200</v>
+      </c>
+      <c r="O1" t="s">
+        <v>201</v>
+      </c>
+      <c r="P1" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>180</v>
+      </c>
+      <c r="R1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="K2" t="s">
+        <v>197</v>
+      </c>
+      <c r="L2" t="s">
+        <v>202</v>
+      </c>
+      <c r="M2" t="s">
+        <v>203</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="O2" t="s">
+        <v>205</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>208</v>
+      </c>
+      <c r="R2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="P2" r:id="rId1" xr:uid="{807B2028-577F-45FF-8D9F-2BB75814B213}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B26CB9A0-785F-4428-A681-554B40CB2D7A}">
+  <dimension ref="A1:W2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.7109375" customWidth="1"/>
+    <col min="23" max="23" width="12.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F1" t="s">
+        <v>213</v>
+      </c>
+      <c r="G1" t="s">
+        <v>214</v>
+      </c>
+      <c r="H1" t="s">
+        <v>215</v>
+      </c>
+      <c r="I1" t="s">
+        <v>216</v>
+      </c>
+      <c r="J1" t="s">
+        <v>217</v>
+      </c>
+      <c r="K1" t="s">
+        <v>218</v>
+      </c>
+      <c r="L1" t="s">
+        <v>219</v>
+      </c>
+      <c r="M1" t="s">
+        <v>220</v>
+      </c>
+      <c r="N1" t="s">
+        <v>221</v>
+      </c>
+      <c r="O1" t="s">
+        <v>222</v>
+      </c>
+      <c r="P1" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>224</v>
+      </c>
+      <c r="R1" t="s">
+        <v>225</v>
+      </c>
+      <c r="S1" t="s">
+        <v>226</v>
+      </c>
+      <c r="T1" t="s">
+        <v>227</v>
+      </c>
+      <c r="U1" t="s">
+        <v>206</v>
+      </c>
+      <c r="V1" t="s">
+        <v>180</v>
+      </c>
+      <c r="W1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="s">
+        <v>229</v>
+      </c>
+      <c r="L2" t="s">
+        <v>230</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="P2" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>235</v>
+      </c>
+      <c r="R2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="V2" t="s">
+        <v>208</v>
+      </c>
+      <c r="W2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{5373313A-0822-4C8A-96F4-8E552924493A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/test/resources/data/PPD/testData.xlsx
+++ b/src/test/resources/data/PPD/testData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wsib-my.sharepoint.com/personal/kiran_kangula_wsib_on_ca/Documents/Documents/Automation/DigitalClaims/src/test/resources/data/PPD/"/>
     </mc:Choice>
@@ -24,7 +24,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="674" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="253">
   <si>
     <t>ReferenceNumber</t>
   </si>
@@ -754,12 +754,61 @@
   </si>
   <si>
     <t>Clothing</t>
+  </si>
+  <si>
+    <t>85129497</t>
+  </si>
+  <si>
+    <t>32651050</t>
+  </si>
+  <si>
+    <t>313457</t>
+  </si>
+  <si>
+    <t>85129503</t>
+  </si>
+  <si>
+    <t>32651060</t>
+  </si>
+  <si>
+    <t>054934</t>
+  </si>
+  <si>
+    <t>85129504</t>
+  </si>
+  <si>
+    <t>32651062</t>
+  </si>
+  <si>
+    <t>147179</t>
+  </si>
+  <si>
+    <t>85129506</t>
+  </si>
+  <si>
+    <t>85129507</t>
+  </si>
+  <si>
+    <t>32651065</t>
+  </si>
+  <si>
+    <t>312834</t>
+  </si>
+  <si>
+    <t>85129508</t>
+  </si>
+  <si>
+    <t>32651067</t>
+  </si>
+  <si>
+    <t>386968</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1266,9 +1315,9 @@
   <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" customWidth="true" width="16.42578125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="11.5703125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="7.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1295,76 +1344,76 @@
   <dimension ref="A1:BY2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.42578125" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="47.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="47.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="9" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="52" max="54" width="28" customWidth="1"/>
-    <col min="55" max="55" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="42.140625" bestFit="1" customWidth="1"/>
-    <col min="58" max="59" width="33.85546875" customWidth="1"/>
-    <col min="60" max="60" width="47.42578125" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="33.85546875" customWidth="1"/>
-    <col min="63" max="63" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="25.140625" customWidth="1"/>
-    <col min="65" max="65" width="14.7109375" customWidth="1"/>
-    <col min="66" max="66" width="20" customWidth="1"/>
-    <col min="67" max="67" width="33.85546875" customWidth="1"/>
-    <col min="68" max="68" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="33.85546875" customWidth="1"/>
-    <col min="70" max="71" width="23" customWidth="1"/>
-    <col min="72" max="72" width="18.42578125" customWidth="1"/>
-    <col min="73" max="73" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="74" max="75" width="19" bestFit="1" customWidth="1"/>
-    <col min="76" max="78" width="33.85546875" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="17.7109375"/>
+    <col min="2" max="2" customWidth="true" width="16.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="14.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="13.85546875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="13.42578125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="9.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="20.42578125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="10.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="9.7109375"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="9.42578125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="7.5703125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="14.7109375"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="10.85546875"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="47.42578125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="14.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="22.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="47.42578125"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="8.0"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="15.7109375"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="18.5703125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="16.42578125"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="17.7109375"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" width="19.7109375"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="19.85546875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="19.42578125"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="23.85546875"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" width="12.85546875"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="15.7109375"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" width="19.5703125"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" width="15.140625"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" width="13.7109375"/>
+    <col min="38" max="38" bestFit="true" customWidth="true" width="16.42578125"/>
+    <col min="39" max="39" bestFit="true" customWidth="true" width="14.42578125"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" width="13.42578125"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" width="9.0"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" width="16.140625"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" width="17.7109375"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" width="17.28515625"/>
+    <col min="45" max="45" bestFit="true" customWidth="true" width="15.7109375"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" width="21.7109375"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" width="12.28515625"/>
+    <col min="48" max="48" bestFit="true" customWidth="true" width="13.85546875"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" width="21.42578125"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" width="17.28515625"/>
+    <col min="51" max="51" bestFit="true" customWidth="true" width="25.28515625"/>
+    <col min="52" max="54" customWidth="true" width="28.0"/>
+    <col min="55" max="55" bestFit="true" customWidth="true" width="23.5703125"/>
+    <col min="56" max="56" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="57" max="57" bestFit="true" customWidth="true" width="42.140625"/>
+    <col min="58" max="59" customWidth="true" width="33.85546875"/>
+    <col min="60" max="60" bestFit="true" customWidth="true" width="47.42578125"/>
+    <col min="61" max="61" bestFit="true" customWidth="true" width="21.7109375"/>
+    <col min="62" max="62" customWidth="true" width="33.85546875"/>
+    <col min="63" max="63" bestFit="true" customWidth="true" width="10.140625"/>
+    <col min="64" max="64" customWidth="true" width="25.140625"/>
+    <col min="65" max="65" customWidth="true" width="14.7109375"/>
+    <col min="66" max="66" customWidth="true" width="20.0"/>
+    <col min="67" max="67" customWidth="true" width="33.85546875"/>
+    <col min="68" max="68" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="69" max="69" customWidth="true" width="33.85546875"/>
+    <col min="70" max="71" customWidth="true" width="23.0"/>
+    <col min="72" max="72" customWidth="true" width="18.42578125"/>
+    <col min="73" max="73" bestFit="true" customWidth="true" width="36.85546875"/>
+    <col min="74" max="75" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="76" max="78" customWidth="true" width="33.85546875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:77" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -1602,75 +1651,75 @@
     </row>
     <row r="2" spans="1:77" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="B2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>241</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>161</v>
       </c>
-      <c r="D2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" t="s" s="0">
+        <v>242</v>
+      </c>
+      <c r="E2" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="G2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>160</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" t="s" s="0">
         <v>23</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" t="s" s="0">
         <v>160</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S2" t="s" s="0">
         <v>27</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U2" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" t="s" s="0">
         <v>43</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="X2" t="s">
+      <c r="X2" t="s" s="0">
         <v>25</v>
       </c>
       <c r="Y2" s="1" t="s">
@@ -1682,31 +1731,31 @@
       <c r="AA2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AC2" t="s" s="0">
         <v>47</v>
       </c>
       <c r="AD2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AE2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG2" t="s">
+      <c r="AE2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="AF2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="AG2" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="AH2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AI2" t="s">
+      <c r="AH2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="AI2" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AJ2" t="s" s="0">
         <v>57</v>
       </c>
       <c r="AK2" s="1" t="s">
@@ -1718,118 +1767,118 @@
       <c r="AM2" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AN2" t="s" s="0">
         <v>59</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AO2" t="s" s="0">
         <v>60</v>
       </c>
-      <c r="AP2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AQ2" t="s">
+      <c r="AP2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="AQ2" t="s" s="0">
         <v>66</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AR2" t="s" s="0">
         <v>67</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AS2" t="s" s="0">
         <v>68</v>
       </c>
       <c r="AT2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AU2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AV2" t="s">
+      <c r="AU2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="AV2" t="s" s="0">
         <v>17</v>
       </c>
       <c r="AW2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AX2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AY2" t="s">
+      <c r="AX2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="AY2" t="s" s="0">
         <v>76</v>
       </c>
-      <c r="AZ2" t="s">
-        <v>17</v>
-      </c>
-      <c r="BA2" t="s">
+      <c r="AZ2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="BA2" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BB2" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BC2" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BD2" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BE2" t="s" s="0">
         <v>85</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BF2" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BG2" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BH2" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="BI2" t="s">
-        <v>17</v>
-      </c>
-      <c r="BJ2" t="s">
+      <c r="BI2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="BJ2" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="BK2" t="s">
-        <v>17</v>
-      </c>
-      <c r="BL2" t="s">
+      <c r="BK2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="BL2" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BM2" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="BN2" t="s">
+      <c r="BN2" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="BO2" t="s">
-        <v>17</v>
-      </c>
-      <c r="BP2" t="s">
+      <c r="BO2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="BP2" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BQ2" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BR2" t="s" s="0">
         <v>106</v>
       </c>
-      <c r="BS2" t="s">
+      <c r="BS2" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BT2" t="s">
-        <v>17</v>
-      </c>
-      <c r="BU2" t="s">
+      <c r="BT2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="BU2" t="s" s="0">
         <v>110</v>
       </c>
-      <c r="BV2" t="s">
-        <v>17</v>
-      </c>
-      <c r="BW2" t="s">
-        <v>17</v>
-      </c>
-      <c r="BX2" t="s">
+      <c r="BV2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="BW2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="BX2" t="s" s="0">
         <v>114</v>
       </c>
-      <c r="BY2" t="s">
+      <c r="BY2" t="s" s="0">
         <v>17</v>
       </c>
     </row>
@@ -1856,74 +1905,74 @@
   <dimension ref="A1:BW2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="47.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="47.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="8" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="19.85546875" customWidth="1"/>
-    <col min="39" max="39" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="50" max="52" width="28" customWidth="1"/>
-    <col min="53" max="53" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="42.140625" bestFit="1" customWidth="1"/>
-    <col min="56" max="57" width="33.85546875" customWidth="1"/>
-    <col min="58" max="58" width="47.42578125" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="33.85546875" customWidth="1"/>
-    <col min="61" max="61" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="25.140625" customWidth="1"/>
-    <col min="63" max="63" width="14.7109375" customWidth="1"/>
-    <col min="64" max="64" width="20" customWidth="1"/>
-    <col min="65" max="65" width="33.85546875" customWidth="1"/>
-    <col min="66" max="66" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="33.85546875" customWidth="1"/>
-    <col min="68" max="69" width="23" customWidth="1"/>
-    <col min="70" max="70" width="18.42578125" customWidth="1"/>
-    <col min="71" max="71" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="72" max="73" width="19" bestFit="1" customWidth="1"/>
-    <col min="74" max="76" width="33.85546875" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="17.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="13.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="4.140625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="14.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="33.85546875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="13.42578125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="9.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="20.42578125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="10.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="9.7109375"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="9.42578125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="7.5703125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="14.7109375"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="10.85546875"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="47.42578125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="14.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="22.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="47.42578125"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="8.0"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="15.7109375"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="18.5703125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="16.42578125"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="17.7109375"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" width="19.7109375"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="19.85546875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="19.42578125"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="23.85546875"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" width="12.85546875"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="15.7109375"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" width="19.5703125"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" width="15.140625"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" width="19.85546875"/>
+    <col min="38" max="38" customWidth="true" width="19.85546875"/>
+    <col min="39" max="39" bestFit="true" customWidth="true" width="15.140625"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" width="16.140625"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" width="17.7109375"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" width="17.28515625"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" width="15.7109375"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" width="21.7109375"/>
+    <col min="45" max="45" bestFit="true" customWidth="true" width="12.28515625"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" width="13.85546875"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" width="21.42578125"/>
+    <col min="48" max="48" bestFit="true" customWidth="true" width="17.28515625"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" width="25.28515625"/>
+    <col min="50" max="52" customWidth="true" width="28.0"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" width="23.5703125"/>
+    <col min="54" max="54" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="55" max="55" bestFit="true" customWidth="true" width="42.140625"/>
+    <col min="56" max="57" customWidth="true" width="33.85546875"/>
+    <col min="58" max="58" bestFit="true" customWidth="true" width="47.42578125"/>
+    <col min="59" max="59" bestFit="true" customWidth="true" width="21.7109375"/>
+    <col min="60" max="60" customWidth="true" width="33.85546875"/>
+    <col min="61" max="61" bestFit="true" customWidth="true" width="10.140625"/>
+    <col min="62" max="62" customWidth="true" width="25.140625"/>
+    <col min="63" max="63" customWidth="true" width="14.7109375"/>
+    <col min="64" max="64" customWidth="true" width="20.0"/>
+    <col min="65" max="65" customWidth="true" width="33.85546875"/>
+    <col min="66" max="66" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="67" max="67" customWidth="true" width="33.85546875"/>
+    <col min="68" max="69" customWidth="true" width="23.0"/>
+    <col min="70" max="70" customWidth="true" width="18.42578125"/>
+    <col min="71" max="71" bestFit="true" customWidth="true" width="36.85546875"/>
+    <col min="72" max="73" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="74" max="76" customWidth="true" width="33.85546875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:75" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2154,76 +2203,76 @@
       </c>
     </row>
     <row r="2" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>162</v>
-      </c>
-      <c r="B2" t="s">
-        <v>163</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>244</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>161</v>
       </c>
-      <c r="D2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" t="s" s="0">
+        <v>245</v>
+      </c>
+      <c r="E2" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="s" s="0">
         <v>119</v>
       </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="G2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>160</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" t="s" s="0">
         <v>23</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" t="s" s="0">
         <v>160</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="S2" t="s">
+      <c r="S2" t="s" s="0">
         <v>27</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U2" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" t="s" s="0">
         <v>43</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="X2" t="s">
+      <c r="X2" t="s" s="0">
         <v>25</v>
       </c>
       <c r="Y2" s="1" t="s">
@@ -2235,148 +2284,148 @@
       <c r="AA2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AC2" t="s" s="0">
         <v>47</v>
       </c>
       <c r="AD2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AE2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG2" t="s">
+      <c r="AE2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="AF2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="AG2" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="AH2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AI2" t="s">
+      <c r="AH2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="AI2" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AJ2" t="s" s="0">
         <v>57</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AK2" t="s" s="0">
         <v>123</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AL2" t="s" s="0">
         <v>124</v>
       </c>
       <c r="AM2" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AN2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AO2" t="s">
+      <c r="AN2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="AO2" t="s" s="0">
         <v>66</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AP2" t="s" s="0">
         <v>67</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AQ2" t="s" s="0">
         <v>68</v>
       </c>
       <c r="AR2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AS2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AT2" t="s">
+      <c r="AS2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="AT2" t="s" s="0">
         <v>17</v>
       </c>
       <c r="AU2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AV2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AW2" t="s">
+      <c r="AV2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="AW2" t="s" s="0">
         <v>76</v>
       </c>
-      <c r="AX2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AY2" t="s">
+      <c r="AX2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="AY2" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="AZ2" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BA2" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BB2" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BC2" t="s" s="0">
         <v>85</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BD2" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BE2" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BF2" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="BG2" t="s">
-        <v>17</v>
-      </c>
-      <c r="BH2" t="s">
+      <c r="BG2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="BH2" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="BI2" t="s">
-        <v>17</v>
-      </c>
-      <c r="BJ2" t="s">
+      <c r="BI2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="BJ2" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BK2" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BL2" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="BM2" t="s">
-        <v>17</v>
-      </c>
-      <c r="BN2" t="s">
+      <c r="BM2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="BN2" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BO2" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BP2" t="s" s="0">
         <v>106</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BQ2" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BR2" t="s">
-        <v>17</v>
-      </c>
-      <c r="BS2" t="s">
+      <c r="BR2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="BS2" t="s" s="0">
         <v>110</v>
       </c>
-      <c r="BT2" t="s">
-        <v>17</v>
-      </c>
-      <c r="BU2" t="s">
-        <v>17</v>
-      </c>
-      <c r="BV2" t="s">
+      <c r="BT2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="BU2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="BV2" t="s" s="0">
         <v>114</v>
       </c>
-      <c r="BW2" t="s">
+      <c r="BW2" t="s" s="0">
         <v>17</v>
       </c>
     </row>
@@ -2402,74 +2451,74 @@
   <dimension ref="A1:BX2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="47.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="47.42578125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="15.140625" customWidth="1"/>
-    <col min="39" max="39" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="9" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="51" max="53" width="28" customWidth="1"/>
-    <col min="54" max="54" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="42.140625" bestFit="1" customWidth="1"/>
-    <col min="57" max="58" width="33.85546875" customWidth="1"/>
-    <col min="59" max="59" width="47.42578125" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="33.85546875" customWidth="1"/>
-    <col min="62" max="62" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="25.140625" customWidth="1"/>
-    <col min="64" max="64" width="14.7109375" customWidth="1"/>
-    <col min="65" max="65" width="20" customWidth="1"/>
-    <col min="66" max="66" width="33.85546875" customWidth="1"/>
-    <col min="67" max="67" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="33.85546875" customWidth="1"/>
-    <col min="69" max="70" width="23" customWidth="1"/>
-    <col min="71" max="71" width="18.42578125" customWidth="1"/>
-    <col min="72" max="72" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="73" max="74" width="19" bestFit="1" customWidth="1"/>
-    <col min="75" max="77" width="33.85546875" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="17.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="13.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="4.140625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="14.7109375"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="24.28515625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="20.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="10.140625"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="9.7109375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="9.42578125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="7.5703125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="14.7109375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="10.85546875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="47.42578125"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="14.85546875"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="22.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="47.42578125"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="8.0"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="15.7109375"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="18.5703125"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="16.42578125"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="17.7109375"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="19.7109375"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" width="19.85546875"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="19.42578125"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="23.85546875"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="12.85546875"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" width="15.7109375"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" width="19.5703125"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" width="17.28515625"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" width="15.140625"/>
+    <col min="37" max="38" customWidth="true" width="15.140625"/>
+    <col min="39" max="39" bestFit="true" customWidth="true" width="13.42578125"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" width="9.0"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" width="16.140625"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" width="17.7109375"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" width="17.28515625"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" width="15.7109375"/>
+    <col min="45" max="45" bestFit="true" customWidth="true" width="21.7109375"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" width="12.28515625"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" width="13.85546875"/>
+    <col min="48" max="48" bestFit="true" customWidth="true" width="21.42578125"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" width="17.28515625"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" width="25.28515625"/>
+    <col min="51" max="53" customWidth="true" width="28.0"/>
+    <col min="54" max="54" bestFit="true" customWidth="true" width="23.5703125"/>
+    <col min="55" max="55" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="56" max="56" bestFit="true" customWidth="true" width="42.140625"/>
+    <col min="57" max="58" customWidth="true" width="33.85546875"/>
+    <col min="59" max="59" bestFit="true" customWidth="true" width="47.42578125"/>
+    <col min="60" max="60" bestFit="true" customWidth="true" width="21.7109375"/>
+    <col min="61" max="61" customWidth="true" width="33.85546875"/>
+    <col min="62" max="62" bestFit="true" customWidth="true" width="10.140625"/>
+    <col min="63" max="63" customWidth="true" width="25.140625"/>
+    <col min="64" max="64" customWidth="true" width="14.7109375"/>
+    <col min="65" max="65" customWidth="true" width="20.0"/>
+    <col min="66" max="66" customWidth="true" width="33.85546875"/>
+    <col min="67" max="67" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="68" max="68" customWidth="true" width="33.85546875"/>
+    <col min="69" max="70" customWidth="true" width="23.0"/>
+    <col min="71" max="71" customWidth="true" width="18.42578125"/>
+    <col min="72" max="72" bestFit="true" customWidth="true" width="36.85546875"/>
+    <col min="73" max="74" bestFit="true" customWidth="true" width="19.0"/>
+    <col min="75" max="77" customWidth="true" width="33.85546875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:76" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2703,73 +2752,73 @@
       </c>
     </row>
     <row r="2" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>246</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>174</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" t="s" s="0">
         <v>161</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>175</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="s" s="0">
         <v>126</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" t="s" s="0">
         <v>127</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>160</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" t="s" s="0">
         <v>23</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" t="s" s="0">
         <v>160</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2" t="s" s="0">
         <v>27</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U2" t="s" s="0">
         <v>43</v>
       </c>
       <c r="V2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" t="s" s="0">
         <v>25</v>
       </c>
       <c r="X2" s="1" t="s">
@@ -2781,31 +2830,31 @@
       <c r="Z2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AA2" t="s" s="0">
         <v>46</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" t="s" s="0">
         <v>47</v>
       </c>
       <c r="AC2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AD2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AF2" t="s">
+      <c r="AD2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="AE2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="AF2" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="AG2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AH2" t="s">
+      <c r="AG2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="AH2" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AI2" t="s" s="0">
         <v>57</v>
       </c>
       <c r="AJ2" s="1" t="s">
@@ -2817,118 +2866,118 @@
       <c r="AL2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AM2" t="s" s="0">
         <v>59</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AN2" t="s" s="0">
         <v>60</v>
       </c>
-      <c r="AO2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AP2" t="s">
+      <c r="AO2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="AP2" t="s" s="0">
         <v>66</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AQ2" t="s" s="0">
         <v>67</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AR2" t="s" s="0">
         <v>68</v>
       </c>
       <c r="AS2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AT2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AU2" t="s">
+      <c r="AT2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="AU2" t="s" s="0">
         <v>17</v>
       </c>
       <c r="AV2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AW2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AX2" t="s">
+      <c r="AW2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="AX2" t="s" s="0">
         <v>76</v>
       </c>
-      <c r="AY2" t="s">
-        <v>17</v>
-      </c>
-      <c r="AZ2" t="s">
+      <c r="AY2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="AZ2" t="s" s="0">
         <v>90</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BA2" t="s" s="0">
         <v>91</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BB2" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BC2" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BD2" t="s" s="0">
         <v>85</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BE2" t="s" s="0">
         <v>87</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BF2" t="s" s="0">
         <v>89</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BG2" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="BH2" t="s">
-        <v>17</v>
-      </c>
-      <c r="BI2" t="s">
+      <c r="BH2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="BI2" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="BJ2" t="s">
-        <v>17</v>
-      </c>
-      <c r="BK2" t="s">
+      <c r="BJ2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="BK2" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="BL2" t="s">
+      <c r="BL2" t="s" s="0">
         <v>99</v>
       </c>
-      <c r="BM2" t="s">
+      <c r="BM2" t="s" s="0">
         <v>100</v>
       </c>
-      <c r="BN2" t="s">
-        <v>17</v>
-      </c>
-      <c r="BO2" t="s">
+      <c r="BN2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="BO2" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BP2" t="s" s="0">
         <v>105</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BQ2" t="s" s="0">
         <v>106</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BR2" t="s" s="0">
         <v>108</v>
       </c>
-      <c r="BS2" t="s">
-        <v>17</v>
-      </c>
-      <c r="BT2" t="s">
+      <c r="BS2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="BT2" t="s" s="0">
         <v>110</v>
       </c>
-      <c r="BU2" t="s">
-        <v>17</v>
-      </c>
-      <c r="BV2" t="s">
-        <v>17</v>
-      </c>
-      <c r="BW2" t="s">
+      <c r="BU2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="BV2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="BW2" t="s" s="0">
         <v>114</v>
       </c>
-      <c r="BX2" t="s">
+      <c r="BX2" t="s" s="0">
         <v>17</v>
       </c>
     </row>
@@ -2957,34 +3006,34 @@
   <dimension ref="A1:AH2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="47.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="47.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="18.42578125" customWidth="1"/>
-    <col min="24" max="24" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="19.5703125" customWidth="1"/>
-    <col min="30" max="32" width="17.28515625" customWidth="1"/>
-    <col min="33" max="33" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="33.85546875" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="17.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="13.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="4.140625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="23.28515625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="10.140625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="9.7109375"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="9.42578125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="7.5703125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="14.7109375"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="47.42578125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="14.85546875"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="22.85546875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="47.42578125"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="8.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="15.7109375"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="12.85546875"/>
+    <col min="22" max="23" customWidth="true" width="18.42578125"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="19.5703125"/>
+    <col min="27" max="29" customWidth="true" width="19.5703125"/>
+    <col min="30" max="32" customWidth="true" width="17.28515625"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" width="19.85546875"/>
+    <col min="34" max="35" customWidth="true" width="33.85546875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3092,58 +3141,58 @@
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>176</v>
-      </c>
-      <c r="B2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>247</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>248</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>161</v>
       </c>
-      <c r="D2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" t="s" s="0">
+        <v>249</v>
+      </c>
+      <c r="E2" t="s" s="0">
         <v>133</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="s" s="0">
         <v>141</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" t="s" s="0">
         <v>134</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" t="s" s="0">
         <v>23</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" t="s" s="0">
         <v>27</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2" t="s" s="0">
         <v>43</v>
       </c>
       <c r="S2" s="1" t="s">
@@ -3152,46 +3201,46 @@
       <c r="T2" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="U2" t="s">
-        <v>17</v>
-      </c>
-      <c r="V2" t="s">
+      <c r="U2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="V2" t="s" s="0">
         <v>141</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" t="s" s="0">
         <v>141</v>
       </c>
-      <c r="X2" t="s">
+      <c r="X2" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="Y2" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z2" t="s">
+      <c r="Y2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="Z2" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AA2" t="s" s="0">
         <v>143</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AC2" t="s" s="0">
         <v>145</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AD2" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AE2" t="s" s="0">
         <v>148</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AF2" t="s" s="0">
         <v>150</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AG2" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AH2" t="s" s="0">
         <v>114</v>
       </c>
     </row>
@@ -3212,34 +3261,34 @@
   <dimension ref="A1:AH2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="47.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="47.42578125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="18.42578125" customWidth="1"/>
-    <col min="24" max="24" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="29" width="19.5703125" customWidth="1"/>
-    <col min="30" max="32" width="17.28515625" customWidth="1"/>
-    <col min="33" max="33" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="33.85546875" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="17.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="13.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="4.85546875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="4.140625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="23.28515625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="10.140625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="9.7109375"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="9.42578125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="7.5703125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="14.7109375"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="47.42578125"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="14.85546875"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="22.85546875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="47.42578125"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="8.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="15.7109375"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="12.85546875"/>
+    <col min="22" max="23" customWidth="true" width="18.42578125"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="19.5703125"/>
+    <col min="27" max="29" customWidth="true" width="19.5703125"/>
+    <col min="30" max="32" customWidth="true" width="17.28515625"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" width="19.85546875"/>
+    <col min="34" max="35" customWidth="true" width="33.85546875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3347,58 +3396,58 @@
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="A2" t="s" s="0">
+        <v>250</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>251</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>161</v>
       </c>
-      <c r="D2" t="s">
-        <v>169</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" t="s" s="0">
+        <v>252</v>
+      </c>
+      <c r="E2" t="s" s="0">
         <v>133</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="s" s="0">
         <v>141</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" t="s" s="0">
         <v>156</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" t="s" s="0">
         <v>23</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" t="s" s="0">
         <v>27</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" t="s" s="0">
         <v>80</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2" t="s" s="0">
         <v>43</v>
       </c>
       <c r="S2" s="1" t="s">
@@ -3407,46 +3456,46 @@
       <c r="T2" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="U2" t="s">
-        <v>17</v>
-      </c>
-      <c r="V2" t="s">
+      <c r="U2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="V2" t="s" s="0">
         <v>141</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" t="s" s="0">
         <v>141</v>
       </c>
-      <c r="X2" t="s">
+      <c r="X2" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="Y2" t="s">
-        <v>17</v>
-      </c>
-      <c r="Z2" t="s">
+      <c r="Y2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="Z2" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AA2" t="s" s="0">
         <v>143</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AC2" t="s" s="0">
         <v>145</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AD2" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AE2" t="s" s="0">
         <v>148</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AF2" t="s" s="0">
         <v>150</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AG2" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AH2" t="s" s="0">
         <v>114</v>
       </c>
     </row>
@@ -3463,74 +3512,74 @@
   <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="10" width="11.140625" customWidth="1"/>
-    <col min="11" max="11" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.7109375" customWidth="1"/>
-    <col min="18" max="18" width="12.42578125" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="12.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.140625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="15.5703125"/>
+    <col min="5" max="10" customWidth="true" width="11.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="28.85546875"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="18.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="24.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="21.0"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="19.28515625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="25.28515625"/>
+    <col min="17" max="17" customWidth="true" width="10.7109375"/>
+    <col min="18" max="18" customWidth="true" width="12.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>177</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>178</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>179</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>182</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>187</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>188</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>190</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>191</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>192</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" t="s" s="0">
         <v>196</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" t="s" s="0">
         <v>198</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" t="s" s="0">
         <v>199</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" t="s" s="0">
         <v>200</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" t="s" s="0">
         <v>201</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" t="s" s="0">
         <v>206</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" t="s" s="0">
         <v>180</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" t="s" s="0">
         <v>181</v>
       </c>
     </row>
@@ -3538,46 +3587,46 @@
       <c r="A2" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>185</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" t="s" s="0">
         <v>183</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" t="s" s="0">
         <v>193</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" t="s" s="0">
         <v>194</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" t="s" s="0">
         <v>197</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" t="s" s="0">
         <v>202</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" t="s" s="0">
         <v>203</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="O2" t="s">
+      <c r="O2" t="s" s="0">
         <v>205</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" t="s" s="0">
         <v>208</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2" t="s" s="0">
         <v>209</v>
       </c>
     </row>
@@ -3595,99 +3644,99 @@
   <dimension ref="A1:W2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.7109375" customWidth="1"/>
-    <col min="23" max="23" width="12.42578125" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="12.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="12.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.140625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="13.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="7.5703125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="10.85546875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="18.42578125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="11.28515625"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="18.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="24.140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="20.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="12.28515625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="10.7109375"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="12.28515625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="13.28515625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="10.85546875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="12.7109375"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="12.140625"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="10.5703125"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="25.28515625"/>
+    <col min="22" max="22" customWidth="true" width="10.7109375"/>
+    <col min="23" max="23" customWidth="true" width="12.42578125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" t="s" s="0">
         <v>177</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>178</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>179</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>210</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>212</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>213</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>214</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>215</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>216</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>217</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" t="s" s="0">
         <v>218</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" t="s" s="0">
         <v>219</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" t="s" s="0">
         <v>220</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" t="s" s="0">
         <v>221</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" t="s" s="0">
         <v>222</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" t="s" s="0">
         <v>223</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" t="s" s="0">
         <v>224</v>
       </c>
-      <c r="R1" t="s">
+      <c r="R1" t="s" s="0">
         <v>225</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" t="s" s="0">
         <v>226</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" t="s" s="0">
         <v>227</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" t="s" s="0">
         <v>206</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" t="s" s="0">
         <v>180</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" t="s" s="0">
         <v>181</v>
       </c>
     </row>
@@ -3695,7 +3744,7 @@
       <c r="A2" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="0">
         <v>185</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -3704,28 +3753,28 @@
       <c r="D2" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s" s="0">
         <v>17</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="H2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="H2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="K2" t="s" s="0">
         <v>229</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" t="s" s="0">
         <v>230</v>
       </c>
       <c r="M2" s="1" t="s">
@@ -3737,28 +3786,28 @@
       <c r="O2" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" t="s" s="0">
         <v>234</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="Q2" t="s" s="0">
         <v>235</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R2" t="s" s="0">
         <v>43</v>
       </c>
-      <c r="S2" t="s">
-        <v>17</v>
-      </c>
-      <c r="T2" t="s">
+      <c r="S2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="T2" t="s" s="0">
         <v>17</v>
       </c>
       <c r="U2" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" t="s" s="0">
         <v>208</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" t="s" s="0">
         <v>236</v>
       </c>
     </row>

--- a/src/test/resources/data/PPD/testData.xlsx
+++ b/src/test/resources/data/PPD/testData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wsib-my.sharepoint.com/personal/kiran_kangula_wsib_on_ca/Documents/Documents/Automation/DigitalClaims/src/test/resources/data/PPD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="164" documentId="13_ncr:1_{A3C00A53-B60F-4FFA-AC45-FA356BAFF82F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C6BFF07-20B3-4194-BA25-1D5915810661}"/>
+  <xr:revisionPtr revIDLastSave="142" documentId="14_{9D299995-2E00-4E35-9164-CFF982FDA28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6017DE29-D0D1-4F50-8099-A5854FA219DB}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GWCC" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="eForm6_Other" sheetId="6" r:id="rId6"/>
     <sheet name="WT" sheetId="7" r:id="rId7"/>
     <sheet name="CAA" sheetId="8" r:id="rId8"/>
+    <sheet name="NIHL" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1258" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="308">
   <si>
     <t>ReferenceNumber</t>
   </si>
@@ -531,51 +532,6 @@
     <t>01/Jan/2000</t>
   </si>
   <si>
-    <t>85129186</t>
-  </si>
-  <si>
-    <t>32650732</t>
-  </si>
-  <si>
-    <t>153486</t>
-  </si>
-  <si>
-    <t>32650738</t>
-  </si>
-  <si>
-    <t>894018</t>
-  </si>
-  <si>
-    <t>85129191</t>
-  </si>
-  <si>
-    <t>32650740</t>
-  </si>
-  <si>
-    <t>968191</t>
-  </si>
-  <si>
-    <t>85129340</t>
-  </si>
-  <si>
-    <t>32650889</t>
-  </si>
-  <si>
-    <t>002676</t>
-  </si>
-  <si>
-    <t>85129342</t>
-  </si>
-  <si>
-    <t>32650891</t>
-  </si>
-  <si>
-    <t>097074</t>
-  </si>
-  <si>
-    <t>85129343</t>
-  </si>
-  <si>
     <t>claimnumber</t>
   </si>
   <si>
@@ -756,52 +712,263 @@
     <t>Clothing</t>
   </si>
   <si>
-    <t>85129497</t>
-  </si>
-  <si>
-    <t>32651050</t>
-  </si>
-  <si>
-    <t>313457</t>
-  </si>
-  <si>
-    <t>85129503</t>
-  </si>
-  <si>
-    <t>32651060</t>
-  </si>
-  <si>
-    <t>054934</t>
-  </si>
-  <si>
-    <t>85129504</t>
-  </si>
-  <si>
-    <t>32651062</t>
-  </si>
-  <si>
-    <t>147179</t>
-  </si>
-  <si>
-    <t>85129506</t>
-  </si>
-  <si>
-    <t>85129507</t>
-  </si>
-  <si>
-    <t>32651065</t>
-  </si>
-  <si>
-    <t>312834</t>
-  </si>
-  <si>
-    <t>85129508</t>
-  </si>
-  <si>
-    <t>32651067</t>
-  </si>
-  <si>
-    <t>386968</t>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>Social Insurance Number</t>
+  </si>
+  <si>
+    <t>Primary Phone</t>
+  </si>
+  <si>
+    <t>Language Preference</t>
+  </si>
+  <si>
+    <t>6478989999</t>
+  </si>
+  <si>
+    <t>HearingLossNoticedYear</t>
+  </si>
+  <si>
+    <t>hearingAidUsageDate</t>
+  </si>
+  <si>
+    <t>01 Jun 2023</t>
+  </si>
+  <si>
+    <t>dateOfFirstAudiogram</t>
+  </si>
+  <si>
+    <t>audiogramClinicName</t>
+  </si>
+  <si>
+    <t>Test Audiogram</t>
+  </si>
+  <si>
+    <t>audiogramClinicAddress</t>
+  </si>
+  <si>
+    <t>140 Erskine Ave
+Toronto, ON M4P 1Z2, Canada</t>
+  </si>
+  <si>
+    <t>audiogramClinicPhoneNumber</t>
+  </si>
+  <si>
+    <t>entAppointmentDate</t>
+  </si>
+  <si>
+    <t>entSpecialistName</t>
+  </si>
+  <si>
+    <t>ENT Specialist</t>
+  </si>
+  <si>
+    <t>entSpecialistAddress</t>
+  </si>
+  <si>
+    <t>entSpecialistPhoneNumber</t>
+  </si>
+  <si>
+    <t>hasVisitedEntSpecialist</t>
+  </si>
+  <si>
+    <t>experienceRingingQuestion</t>
+  </si>
+  <si>
+    <t>ringingEarDuration</t>
+  </si>
+  <si>
+    <t>More than 2 years</t>
+  </si>
+  <si>
+    <t>hasSevereRingingInEar</t>
+  </si>
+  <si>
+    <t>isRingingConstant</t>
+  </si>
+  <si>
+    <t>wearHearingAid</t>
+  </si>
+  <si>
+    <t>Are you retired?</t>
+  </si>
+  <si>
+    <t>Are you currently employed?</t>
+  </si>
+  <si>
+    <t>HazardousNoiseRadio</t>
+  </si>
+  <si>
+    <t>SelfEmployedRadio</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>InsuranceRadio</t>
+  </si>
+  <si>
+    <t>BusinessName</t>
+  </si>
+  <si>
+    <t>BusinessAddress</t>
+  </si>
+  <si>
+    <t>BusinessFrom</t>
+  </si>
+  <si>
+    <t>BusinessTo</t>
+  </si>
+  <si>
+    <t>01 Jun 2024</t>
+  </si>
+  <si>
+    <t>Business Name</t>
+  </si>
+  <si>
+    <t>noisyMachineryOffwork</t>
+  </si>
+  <si>
+    <t>usedNoisyMachinery</t>
+  </si>
+  <si>
+    <t>noisy mechaninh</t>
+  </si>
+  <si>
+    <t>test title</t>
+  </si>
+  <si>
+    <t>EmployedFrom</t>
+  </si>
+  <si>
+    <t>EmployedTo</t>
+  </si>
+  <si>
+    <t>ToolsEquipmentUsed</t>
+  </si>
+  <si>
+    <t>Vehicle testing</t>
+  </si>
+  <si>
+    <t>HoursUsed</t>
+  </si>
+  <si>
+    <t>StillInBusiness</t>
+  </si>
+  <si>
+    <t>RetirementDate</t>
+  </si>
+  <si>
+    <t>140 Erskine Ave, Toronto, ON M4P 1Z2, Canada</t>
+  </si>
+  <si>
+    <t>32715385</t>
+  </si>
+  <si>
+    <t>538583</t>
+  </si>
+  <si>
+    <t>32715400</t>
+  </si>
+  <si>
+    <t>981304</t>
+  </si>
+  <si>
+    <t>32715401</t>
+  </si>
+  <si>
+    <t>071463</t>
+  </si>
+  <si>
+    <t>85244496</t>
+  </si>
+  <si>
+    <t>32715402</t>
+  </si>
+  <si>
+    <t>161736</t>
+  </si>
+  <si>
+    <t>32715403</t>
+  </si>
+  <si>
+    <t>261481</t>
+  </si>
+  <si>
+    <t>32715404</t>
+  </si>
+  <si>
+    <t>337116</t>
+  </si>
+  <si>
+    <t>TOSPWSIB\svc_kfxppd</t>
+  </si>
+  <si>
+    <t>REPORT IND DEAFNESS</t>
+  </si>
+  <si>
+    <t>1/January/1985</t>
+  </si>
+  <si>
+    <t>CAA</t>
+  </si>
+  <si>
+    <t>KKFirstqsdqm</t>
+  </si>
+  <si>
+    <t>KKLastqnxfr</t>
+  </si>
+  <si>
+    <t>85244834</t>
+  </si>
+  <si>
+    <t>85244835</t>
+  </si>
+  <si>
+    <t>85244836</t>
+  </si>
+  <si>
+    <t>85244837</t>
+  </si>
+  <si>
+    <t>85130475</t>
+  </si>
+  <si>
+    <t>KKFirstnsbvs</t>
+  </si>
+  <si>
+    <t>KKLastvafvb</t>
+  </si>
+  <si>
+    <t>85130698</t>
+  </si>
+  <si>
+    <t>85130699</t>
+  </si>
+  <si>
+    <t>85130701</t>
+  </si>
+  <si>
+    <t>85130702</t>
+  </si>
+  <si>
+    <t>KKFirstdejsl</t>
+  </si>
+  <si>
+    <t>KKLastwyoko</t>
+  </si>
+  <si>
+    <t>KKFirstykfea</t>
+  </si>
+  <si>
+    <t>KKLasthmhqe</t>
   </si>
 </sst>
 </file>
@@ -834,12 +1001,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -855,17 +1034,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1312,7 +1507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" width="16.42578125"/>
@@ -1331,9 +1526,20 @@
         <v>159</v>
       </c>
     </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:C1">
-    <cfRule type="duplicateValues" dxfId="16" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1651,16 +1857,16 @@
     </row>
     <row r="2" spans="1:77" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>241</v>
+        <v>276</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>161</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>242</v>
+        <v>277</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>15</v>
@@ -1884,16 +2090,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="P1:T1 A1 V1:XFD1 E1:N1">
-    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1">
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U1">
-    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:D1">
-    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2204,16 +2410,16 @@
     </row>
     <row r="2" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A2" t="s" s="0">
-        <v>243</v>
+        <v>301</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>244</v>
+        <v>278</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>161</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>245</v>
+        <v>279</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>15</v>
@@ -2431,16 +2637,16 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="P1:T1 A1 V1:XFD1 E1:N1">
-    <cfRule type="duplicateValues" dxfId="11" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1">
-    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U1">
-    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:D1">
-    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2753,16 +2959,16 @@
     </row>
     <row r="2" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A2" t="s" s="0">
-        <v>246</v>
+        <v>302</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>174</v>
+        <v>281</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>161</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>175</v>
+        <v>282</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>15</v>
@@ -2983,19 +3189,19 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="AO1:XFD1 A1 O1:S1 U1:AL1 E1:M1">
-    <cfRule type="duplicateValues" dxfId="7" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM1:AN1">
-    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:D1">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3142,16 +3348,16 @@
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" t="s" s="0">
-        <v>247</v>
+        <v>303</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>248</v>
+        <v>283</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>161</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>249</v>
+        <v>284</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>133</v>
@@ -3246,10 +3452,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1 E1:XFD1">
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:D1">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3397,16 +3603,16 @@
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" t="s" s="0">
-        <v>250</v>
+        <v>296</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>251</v>
+        <v>285</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>161</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>252</v>
+        <v>286</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>133</v>
@@ -3501,7 +3707,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3529,105 +3735,105 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s" s="0">
+        <v>162</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>163</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>164</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>167</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>172</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>175</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>176</v>
+      </c>
+      <c r="J1" t="s" s="0">
         <v>177</v>
       </c>
-      <c r="B1" t="s" s="0">
-        <v>178</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>179</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>182</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>187</v>
-      </c>
-      <c r="F1" t="s" s="0">
-        <v>188</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>189</v>
-      </c>
-      <c r="H1" t="s" s="0">
-        <v>190</v>
-      </c>
-      <c r="I1" t="s" s="0">
+      <c r="K1" t="s" s="0">
+        <v>181</v>
+      </c>
+      <c r="L1" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="M1" t="s" s="0">
+        <v>184</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>186</v>
+      </c>
+      <c r="P1" t="s" s="0">
         <v>191</v>
       </c>
-      <c r="J1" t="s" s="0">
-        <v>192</v>
-      </c>
-      <c r="K1" t="s" s="0">
-        <v>196</v>
-      </c>
-      <c r="L1" t="s" s="0">
-        <v>198</v>
-      </c>
-      <c r="M1" t="s" s="0">
-        <v>199</v>
-      </c>
-      <c r="N1" t="s" s="0">
-        <v>200</v>
-      </c>
-      <c r="O1" t="s" s="0">
-        <v>201</v>
-      </c>
-      <c r="P1" t="s" s="0">
-        <v>206</v>
-      </c>
       <c r="Q1" t="s" s="0">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="R1" t="s" s="0">
-        <v>181</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="E2" t="s" s="0">
+        <v>178</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>179</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>182</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>187</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>188</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="O2" t="s" s="0">
+        <v>190</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q2" t="s" s="0">
         <v>193</v>
       </c>
-      <c r="F2" t="s" s="0">
+      <c r="R2" t="s" s="0">
         <v>194</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="K2" t="s" s="0">
-        <v>197</v>
-      </c>
-      <c r="L2" t="s" s="0">
-        <v>202</v>
-      </c>
-      <c r="M2" t="s" s="0">
-        <v>203</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="O2" t="s" s="0">
-        <v>205</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="Q2" t="s" s="0">
-        <v>208</v>
-      </c>
-      <c r="R2" t="s" s="0">
-        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -3671,87 +3877,87 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s" s="0">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="B1" t="s" s="0">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="C1" t="s" s="0">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="D1" t="s" s="0">
+        <v>195</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>197</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>198</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>201</v>
+      </c>
+      <c r="J1" t="s" s="0">
+        <v>202</v>
+      </c>
+      <c r="K1" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="L1" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="M1" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="P1" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="Q1" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="R1" t="s" s="0">
         <v>210</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="S1" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="T1" t="s" s="0">
         <v>212</v>
       </c>
-      <c r="F1" t="s" s="0">
-        <v>213</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>214</v>
-      </c>
-      <c r="H1" t="s" s="0">
-        <v>215</v>
-      </c>
-      <c r="I1" t="s" s="0">
-        <v>216</v>
-      </c>
-      <c r="J1" t="s" s="0">
-        <v>217</v>
-      </c>
-      <c r="K1" t="s" s="0">
-        <v>218</v>
-      </c>
-      <c r="L1" t="s" s="0">
-        <v>219</v>
-      </c>
-      <c r="M1" t="s" s="0">
-        <v>220</v>
-      </c>
-      <c r="N1" t="s" s="0">
-        <v>221</v>
-      </c>
-      <c r="O1" t="s" s="0">
-        <v>222</v>
-      </c>
-      <c r="P1" t="s" s="0">
-        <v>223</v>
-      </c>
-      <c r="Q1" t="s" s="0">
-        <v>224</v>
-      </c>
-      <c r="R1" t="s" s="0">
-        <v>225</v>
-      </c>
-      <c r="S1" t="s" s="0">
-        <v>226</v>
-      </c>
-      <c r="T1" t="s" s="0">
-        <v>227</v>
-      </c>
       <c r="U1" t="s" s="0">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="V1" t="s" s="0">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="W1" t="s" s="0">
-        <v>181</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>17</v>
@@ -3760,7 +3966,7 @@
         <v>17</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="H2" t="s" s="0">
         <v>17</v>
@@ -3772,25 +3978,25 @@
         <v>17</v>
       </c>
       <c r="K2" t="s" s="0">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="L2" t="s" s="0">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="P2" t="s" s="0">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="Q2" t="s" s="0">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="R2" t="s" s="0">
         <v>43</v>
@@ -3802,13 +4008,13 @@
         <v>17</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="V2" t="s" s="0">
-        <v>208</v>
+        <v>290</v>
       </c>
       <c r="W2" t="s" s="0">
-        <v>236</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -3817,4 +4023,352 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{940E15E8-DD0F-406D-92A0-8C299A35101B}">
+  <dimension ref="A1:AU2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" width="22.28515625"/>
+    <col min="2" max="2" customWidth="true" width="21.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="13.28515625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="11.42578125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="23.28515625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="47.42578125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="19.85546875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="22.85546875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="18.5703125"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="20.42578125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="21.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="20.85546875"/>
+    <col min="14" max="14" customWidth="true" width="30.7109375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="28.85546875"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="25.0"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="20.28515625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="18.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="19.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="26.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="29.28515625"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="20.85546875"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="25" max="26" customWidth="true" width="19.85546875"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" width="27.28515625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="14.85546875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="15.28515625"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" width="20.5703125"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="18.5703125"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" width="14.7109375"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" width="13.42578125"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" width="10.85546875"/>
+    <col min="38" max="38" bestFit="true" customWidth="true" width="22.7109375"/>
+    <col min="39" max="39" bestFit="true" customWidth="true" width="19.85546875"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" width="13.85546875"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" width="8.5703125"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" width="12.0"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" width="20.140625"/>
+    <col min="45" max="45" customWidth="true" width="11.85546875"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" width="21.140625"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" width="21.42578125"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A1" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>223</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>225</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>226</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>227</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>229</v>
+      </c>
+      <c r="J1" t="s" s="0">
+        <v>249</v>
+      </c>
+      <c r="K1" t="s" s="0">
+        <v>230</v>
+      </c>
+      <c r="L1" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="M1" t="s" s="0">
+        <v>233</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>235</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>237</v>
+      </c>
+      <c r="P1" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="Q1" t="s" s="0">
+        <v>238</v>
+      </c>
+      <c r="R1" t="s" s="0">
+        <v>239</v>
+      </c>
+      <c r="S1" t="s" s="0">
+        <v>241</v>
+      </c>
+      <c r="T1" t="s" s="0">
+        <v>242</v>
+      </c>
+      <c r="U1" t="s" s="0">
+        <v>244</v>
+      </c>
+      <c r="V1" t="s" s="0">
+        <v>245</v>
+      </c>
+      <c r="W1" t="s" s="0">
+        <v>247</v>
+      </c>
+      <c r="X1" t="s" s="0">
+        <v>248</v>
+      </c>
+      <c r="Y1" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z1" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="AA1" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE1" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="AF1" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="AG1" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="AH1" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="AI1" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="AJ1" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="AK1" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="AL1" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="AM1" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="AN1" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="AO1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AP1" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="AQ1" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="AR1" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="AS1" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="AT1" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="AU1" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="2" spans="1:47" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>306</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>307</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>234</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="R2" t="s" s="0">
+        <v>240</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="U2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="V2" t="s" s="0">
+        <v>246</v>
+      </c>
+      <c r="W2" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="X2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="Y2" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="AA2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="AB2" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="AC2" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE2" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="AF2" t="s" s="0">
+        <v>254</v>
+      </c>
+      <c r="AG2" t="s" s="0">
+        <v>254</v>
+      </c>
+      <c r="AH2" t="s" s="0">
+        <v>261</v>
+      </c>
+      <c r="AI2" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AL2" t="s" s="0">
+        <v>254</v>
+      </c>
+      <c r="AM2" t="s" s="0">
+        <v>264</v>
+      </c>
+      <c r="AN2" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="AO2" t="s" s="0">
+        <v>265</v>
+      </c>
+      <c r="AP2" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="AQ2" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="AR2" t="s" s="0">
+        <v>269</v>
+      </c>
+      <c r="AS2" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="AT2" t="s" s="0">
+        <v>287</v>
+      </c>
+      <c r="AU2" t="s" s="0">
+        <v>288</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:XFD1">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{88CF68CF-863A-4741-8C66-57791459BD62}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+</worksheet>
 </file>
--- a/src/test/resources/data/PPD/testData.xlsx
+++ b/src/test/resources/data/PPD/testData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wsib-my.sharepoint.com/personal/kiran_kangula_wsib_on_ca/Documents/Documents/Automation/DigitalClaims/src/test/resources/data/PPD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="142" documentId="14_{9D299995-2E00-4E35-9164-CFF982FDA28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6017DE29-D0D1-4F50-8099-A5854FA219DB}"/>
+  <xr:revisionPtr revIDLastSave="146" documentId="14_{9D299995-2E00-4E35-9164-CFF982FDA28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8C6A7EE-FD2F-4A1A-A6E4-5F1C20FF1F8A}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GWCC" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="314">
   <si>
     <t>ReferenceNumber</t>
   </si>
@@ -530,9 +530,6 @@
   </si>
   <si>
     <t>01/Jan/2000</t>
-  </si>
-  <si>
-    <t>claimnumber</t>
   </si>
   <si>
     <t>lastname</t>
@@ -887,9 +884,6 @@
     <t>071463</t>
   </si>
   <si>
-    <t>85244496</t>
-  </si>
-  <si>
     <t>32715402</t>
   </si>
   <si>
@@ -920,33 +914,9 @@
     <t>CAA</t>
   </si>
   <si>
-    <t>KKFirstqsdqm</t>
-  </si>
-  <si>
-    <t>KKLastqnxfr</t>
-  </si>
-  <si>
-    <t>85244834</t>
-  </si>
-  <si>
-    <t>85244835</t>
-  </si>
-  <si>
-    <t>85244836</t>
-  </si>
-  <si>
     <t>85244837</t>
   </si>
   <si>
-    <t>85130475</t>
-  </si>
-  <si>
-    <t>KKFirstnsbvs</t>
-  </si>
-  <si>
-    <t>KKLastvafvb</t>
-  </si>
-  <si>
     <t>85130698</t>
   </si>
   <si>
@@ -959,16 +929,64 @@
     <t>85130702</t>
   </si>
   <si>
-    <t>KKFirstdejsl</t>
-  </si>
-  <si>
-    <t>KKLastwyoko</t>
-  </si>
-  <si>
     <t>KKFirstykfea</t>
   </si>
   <si>
     <t>KKLasthmhqe</t>
+  </si>
+  <si>
+    <t>KKFirstaagvy</t>
+  </si>
+  <si>
+    <t>KKLastibnbh</t>
+  </si>
+  <si>
+    <t>KKFirstydzfj</t>
+  </si>
+  <si>
+    <t>KKLastsncde</t>
+  </si>
+  <si>
+    <t>KKFirsttkpfa</t>
+  </si>
+  <si>
+    <t>KKLastqzmvf</t>
+  </si>
+  <si>
+    <t>KKFirstagzie</t>
+  </si>
+  <si>
+    <t>KKLastoupjk</t>
+  </si>
+  <si>
+    <t>KKFirstyhaso</t>
+  </si>
+  <si>
+    <t>KKLastwtswf</t>
+  </si>
+  <si>
+    <t>KKFirstvomgb</t>
+  </si>
+  <si>
+    <t>KKLastkzqwf</t>
+  </si>
+  <si>
+    <t>KKFirsttstlf</t>
+  </si>
+  <si>
+    <t>KKLastsdstq</t>
+  </si>
+  <si>
+    <t>KKFirstykuid</t>
+  </si>
+  <si>
+    <t>KKLastmqrzh</t>
+  </si>
+  <si>
+    <t>KKFirstfpuzr</t>
+  </si>
+  <si>
+    <t>KKLastfletn</t>
   </si>
 </sst>
 </file>
@@ -1528,13 +1546,13 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>161</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -1857,16 +1875,16 @@
     </row>
     <row r="2" spans="1:77" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>161</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>15</v>
@@ -2089,17 +2107,17 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="P1:T1 A1 V1:XFD1 E1:N1">
-    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
+  <conditionalFormatting sqref="B1:D1">
+    <cfRule type="duplicateValues" dxfId="16" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1">
     <cfRule type="duplicateValues" dxfId="15" priority="3"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="P1:T1 A1 V1:XFD1 E1:N1">
+    <cfRule type="duplicateValues" dxfId="14" priority="4"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="U1">
-    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:D1">
-    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2410,16 +2428,16 @@
     </row>
     <row r="2" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A2" t="s" s="0">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>161</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>15</v>
@@ -2636,17 +2654,17 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="P1:T1 A1 V1:XFD1 E1:N1">
-    <cfRule type="duplicateValues" dxfId="12" priority="4"/>
+  <conditionalFormatting sqref="B1:D1">
+    <cfRule type="duplicateValues" dxfId="12" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="O1">
     <cfRule type="duplicateValues" dxfId="11" priority="3"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="P1:T1 A1 V1:XFD1 E1:N1">
+    <cfRule type="duplicateValues" dxfId="10" priority="4"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="U1">
-    <cfRule type="duplicateValues" dxfId="10" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:D1">
-    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2959,16 +2977,16 @@
     </row>
     <row r="2" spans="1:76" x14ac:dyDescent="0.25">
       <c r="A2" t="s" s="0">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>161</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>15</v>
@@ -3188,20 +3206,20 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="AO1:XFD1 A1 O1:S1 U1:AL1 E1:M1">
-    <cfRule type="duplicateValues" dxfId="8" priority="5"/>
+  <conditionalFormatting sqref="B1:D1">
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1">
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T1">
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM1:AN1">
-    <cfRule type="duplicateValues" dxfId="7" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N1">
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T1">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:D1">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
+  <conditionalFormatting sqref="AO1:XFD1 A1 O1:S1 U1:AL1 E1:M1">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3348,16 +3366,16 @@
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" t="s" s="0">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>161</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>133</v>
@@ -3603,16 +3621,16 @@
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A2" t="s" s="0">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="B2" t="s" s="0">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C2" t="s" s="0">
         <v>161</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>133</v>
@@ -3718,7 +3736,7 @@
   <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="12.7109375"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="13.85546875"/>
     <col min="2" max="2" bestFit="true" customWidth="true" width="12.85546875"/>
     <col min="3" max="3" bestFit="true" customWidth="true" width="11.140625"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="15.5703125"/>
@@ -3735,105 +3753,105 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>162</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>163</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
+        <v>166</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>171</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>172</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>173</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>174</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>175</v>
+      </c>
+      <c r="J1" t="s" s="0">
+        <v>176</v>
+      </c>
+      <c r="K1" t="s" s="0">
+        <v>180</v>
+      </c>
+      <c r="L1" t="s" s="0">
+        <v>182</v>
+      </c>
+      <c r="M1" t="s" s="0">
+        <v>183</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>184</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>185</v>
+      </c>
+      <c r="P1" t="s" s="0">
+        <v>190</v>
+      </c>
+      <c r="Q1" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="D1" t="s" s="0">
-        <v>167</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>172</v>
-      </c>
-      <c r="F1" t="s" s="0">
-        <v>173</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>174</v>
-      </c>
-      <c r="H1" t="s" s="0">
-        <v>175</v>
-      </c>
-      <c r="I1" t="s" s="0">
-        <v>176</v>
-      </c>
-      <c r="J1" t="s" s="0">
-        <v>177</v>
-      </c>
-      <c r="K1" t="s" s="0">
-        <v>181</v>
-      </c>
-      <c r="L1" t="s" s="0">
-        <v>183</v>
-      </c>
-      <c r="M1" t="s" s="0">
-        <v>184</v>
-      </c>
-      <c r="N1" t="s" s="0">
-        <v>185</v>
-      </c>
-      <c r="O1" t="s" s="0">
-        <v>186</v>
-      </c>
-      <c r="P1" t="s" s="0">
-        <v>191</v>
-      </c>
-      <c r="Q1" t="s" s="0">
+      <c r="R1" t="s" s="0">
         <v>165</v>
-      </c>
-      <c r="R1" t="s" s="0">
-        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>169</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="C2" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="D2" t="s" s="0">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E2" t="s" s="0">
+        <v>177</v>
+      </c>
+      <c r="F2" t="s" s="0">
         <v>178</v>
       </c>
-      <c r="F2" t="s" s="0">
+      <c r="G2" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="K2" t="s" s="0">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L2" t="s" s="0">
+        <v>186</v>
+      </c>
+      <c r="M2" t="s" s="0">
         <v>187</v>
       </c>
-      <c r="M2" t="s" s="0">
+      <c r="N2" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" t="s" s="0">
         <v>189</v>
       </c>
-      <c r="O2" t="s" s="0">
-        <v>190</v>
-      </c>
       <c r="P2" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q2" t="s" s="0">
         <v>192</v>
       </c>
-      <c r="Q2" t="s" s="0">
+      <c r="R2" t="s" s="0">
         <v>193</v>
-      </c>
-      <c r="R2" t="s" s="0">
-        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -3850,7 +3868,7 @@
   <dimension ref="A1:W2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="12.7109375"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="13.85546875"/>
     <col min="2" max="2" bestFit="true" customWidth="true" width="12.85546875"/>
     <col min="3" max="3" bestFit="true" customWidth="true" width="11.140625"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="13.85546875"/>
@@ -3877,87 +3895,87 @@
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s" s="0">
+        <v>157</v>
+      </c>
+      <c r="B1" t="s" s="0">
         <v>162</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="C1" t="s" s="0">
         <v>163</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="D1" t="s" s="0">
+        <v>194</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>196</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>197</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>198</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>199</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>200</v>
+      </c>
+      <c r="J1" t="s" s="0">
+        <v>201</v>
+      </c>
+      <c r="K1" t="s" s="0">
+        <v>202</v>
+      </c>
+      <c r="L1" t="s" s="0">
+        <v>203</v>
+      </c>
+      <c r="M1" t="s" s="0">
+        <v>204</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>205</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>206</v>
+      </c>
+      <c r="P1" t="s" s="0">
+        <v>207</v>
+      </c>
+      <c r="Q1" t="s" s="0">
+        <v>208</v>
+      </c>
+      <c r="R1" t="s" s="0">
+        <v>209</v>
+      </c>
+      <c r="S1" t="s" s="0">
+        <v>210</v>
+      </c>
+      <c r="T1" t="s" s="0">
+        <v>211</v>
+      </c>
+      <c r="U1" t="s" s="0">
+        <v>190</v>
+      </c>
+      <c r="V1" t="s" s="0">
         <v>164</v>
       </c>
-      <c r="D1" t="s" s="0">
-        <v>195</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>197</v>
-      </c>
-      <c r="F1" t="s" s="0">
-        <v>198</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>199</v>
-      </c>
-      <c r="H1" t="s" s="0">
-        <v>200</v>
-      </c>
-      <c r="I1" t="s" s="0">
-        <v>201</v>
-      </c>
-      <c r="J1" t="s" s="0">
-        <v>202</v>
-      </c>
-      <c r="K1" t="s" s="0">
-        <v>203</v>
-      </c>
-      <c r="L1" t="s" s="0">
-        <v>204</v>
-      </c>
-      <c r="M1" t="s" s="0">
-        <v>205</v>
-      </c>
-      <c r="N1" t="s" s="0">
-        <v>206</v>
-      </c>
-      <c r="O1" t="s" s="0">
-        <v>207</v>
-      </c>
-      <c r="P1" t="s" s="0">
-        <v>208</v>
-      </c>
-      <c r="Q1" t="s" s="0">
-        <v>209</v>
-      </c>
-      <c r="R1" t="s" s="0">
-        <v>210</v>
-      </c>
-      <c r="S1" t="s" s="0">
-        <v>211</v>
-      </c>
-      <c r="T1" t="s" s="0">
-        <v>212</v>
-      </c>
-      <c r="U1" t="s" s="0">
-        <v>191</v>
-      </c>
-      <c r="V1" t="s" s="0">
+      <c r="W1" t="s" s="0">
         <v>165</v>
-      </c>
-      <c r="W1" t="s" s="0">
-        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2" t="s" s="0">
         <v>169</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="C2" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>17</v>
@@ -3966,37 +3984,37 @@
         <v>17</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="K2" t="s" s="0">
         <v>213</v>
       </c>
-      <c r="H2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="J2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="K2" t="s" s="0">
+      <c r="L2" t="s" s="0">
         <v>214</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="M2" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="N2" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="P2" t="s" s="0">
         <v>218</v>
       </c>
-      <c r="P2" t="s" s="0">
+      <c r="Q2" t="s" s="0">
         <v>219</v>
-      </c>
-      <c r="Q2" t="s" s="0">
-        <v>220</v>
       </c>
       <c r="R2" t="s" s="0">
         <v>43</v>
@@ -4008,13 +4026,13 @@
         <v>17</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="V2" t="s" s="0">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="W2" t="s" s="0">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -4080,85 +4098,85 @@
   <sheetData>
     <row r="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A1" t="s" s="0">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B1" t="s" s="0">
         <v>135</v>
       </c>
       <c r="C1" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="D1" t="s" s="0">
         <v>223</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="E1" t="s" s="0">
         <v>224</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>225</v>
       </c>
       <c r="F1" t="s" s="0">
         <v>12</v>
       </c>
       <c r="G1" t="s" s="0">
+        <v>225</v>
+      </c>
+      <c r="H1" t="s" s="0">
         <v>226</v>
       </c>
-      <c r="H1" t="s" s="0">
-        <v>227</v>
-      </c>
       <c r="I1" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="J1" t="s" s="0">
+        <v>248</v>
+      </c>
+      <c r="K1" t="s" s="0">
         <v>229</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="L1" t="s" s="0">
+        <v>231</v>
+      </c>
+      <c r="M1" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>234</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>236</v>
+      </c>
+      <c r="P1" t="s" s="0">
+        <v>242</v>
+      </c>
+      <c r="Q1" t="s" s="0">
+        <v>237</v>
+      </c>
+      <c r="R1" t="s" s="0">
+        <v>238</v>
+      </c>
+      <c r="S1" t="s" s="0">
+        <v>240</v>
+      </c>
+      <c r="T1" t="s" s="0">
+        <v>241</v>
+      </c>
+      <c r="U1" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="V1" t="s" s="0">
+        <v>244</v>
+      </c>
+      <c r="W1" t="s" s="0">
+        <v>246</v>
+      </c>
+      <c r="X1" t="s" s="0">
+        <v>247</v>
+      </c>
+      <c r="Y1" s="5" t="s">
         <v>249</v>
       </c>
-      <c r="K1" t="s" s="0">
-        <v>230</v>
-      </c>
-      <c r="L1" t="s" s="0">
-        <v>232</v>
-      </c>
-      <c r="M1" t="s" s="0">
-        <v>233</v>
-      </c>
-      <c r="N1" t="s" s="0">
-        <v>235</v>
-      </c>
-      <c r="O1" t="s" s="0">
-        <v>237</v>
-      </c>
-      <c r="P1" t="s" s="0">
-        <v>243</v>
-      </c>
-      <c r="Q1" t="s" s="0">
-        <v>238</v>
-      </c>
-      <c r="R1" t="s" s="0">
-        <v>239</v>
-      </c>
-      <c r="S1" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="T1" t="s" s="0">
-        <v>242</v>
-      </c>
-      <c r="U1" t="s" s="0">
-        <v>244</v>
-      </c>
-      <c r="V1" t="s" s="0">
-        <v>245</v>
-      </c>
-      <c r="W1" t="s" s="0">
-        <v>247</v>
-      </c>
-      <c r="X1" t="s" s="0">
-        <v>248</v>
-      </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Z1" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="AA1" s="5" t="s">
         <v>250</v>
-      </c>
-      <c r="Z1" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="AA1" s="5" t="s">
-        <v>251</v>
       </c>
       <c r="AB1" s="5" t="s">
         <v>13</v>
@@ -4170,75 +4188,75 @@
         <v>30</v>
       </c>
       <c r="AE1" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="AF1" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="AF1" s="5" t="s">
-        <v>253</v>
-      </c>
       <c r="AG1" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="AH1" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="AH1" s="5" t="s">
+      <c r="AI1" s="5" t="s">
         <v>256</v>
       </c>
-      <c r="AI1" s="5" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="AJ1" s="5" t="s">
+      <c r="AK1" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="AK1" s="5" t="s">
-        <v>259</v>
-      </c>
       <c r="AL1" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="AM1" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="AM1" s="5" t="s">
-        <v>263</v>
-      </c>
       <c r="AN1" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AO1" s="5" t="s">
         <v>31</v>
       </c>
       <c r="AP1" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="AQ1" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="AQ1" s="5" t="s">
+      <c r="AR1" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="AR1" s="5" t="s">
-        <v>268</v>
-      </c>
       <c r="AS1" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AT1" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="AU1" s="7" t="s">
         <v>165</v>
-      </c>
-      <c r="AU1" s="7" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:47" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="F2" t="s" s="0">
         <v>80</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H2" t="s" s="0">
         <v>26</v>
@@ -4250,16 +4268,16 @@
         <v>17</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="M2" t="s" s="0">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>21</v>
@@ -4268,13 +4286,13 @@
         <v>17</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="R2" t="s" s="0">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="S2" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>21</v>
@@ -4283,7 +4301,7 @@
         <v>17</v>
       </c>
       <c r="V2" t="s" s="0">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="W2" t="s" s="0">
         <v>141</v>
@@ -4295,7 +4313,7 @@
         <v>141</v>
       </c>
       <c r="Z2" s="6" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AA2" t="s" s="0">
         <v>17</v>
@@ -4304,7 +4322,7 @@
         <v>43</v>
       </c>
       <c r="AC2" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AD2" s="1" t="s">
         <v>21</v>
@@ -4313,52 +4331,52 @@
         <v>141</v>
       </c>
       <c r="AF2" t="s" s="0">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AG2" t="s" s="0">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AH2" t="s" s="0">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AI2" s="4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AK2" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AL2" t="s" s="0">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AM2" t="s" s="0">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AN2" t="s" s="0">
         <v>141</v>
       </c>
       <c r="AO2" t="s" s="0">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AR2" t="s" s="0">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AT2" t="s" s="0">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AU2" t="s" s="0">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/data/PPD/testData.xlsx
+++ b/src/test/resources/data/PPD/testData.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wsib-my.sharepoint.com/personal/kiran_kangula_wsib_on_ca/Documents/Documents/Automation/DigitalClaims/src/test/resources/data/PPD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="146" documentId="14_{9D299995-2E00-4E35-9164-CFF982FDA28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8C6A7EE-FD2F-4A1A-A6E4-5F1C20FF1F8A}"/>
+  <xr:revisionPtr revIDLastSave="197" documentId="14_{9D299995-2E00-4E35-9164-CFF982FDA28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{857A3A0E-2661-48E4-A152-27BA3096DFDC}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GWCC" sheetId="1" r:id="rId1"/>
-    <sheet name="eForm6_PI" sheetId="2" r:id="rId2"/>
-    <sheet name="eForm6_Illness" sheetId="3" r:id="rId3"/>
-    <sheet name="eForm6_Mental" sheetId="4" r:id="rId4"/>
-    <sheet name="eForm6_Construction" sheetId="5" r:id="rId5"/>
-    <sheet name="eForm6_Other" sheetId="6" r:id="rId6"/>
-    <sheet name="WT" sheetId="7" r:id="rId7"/>
-    <sheet name="CAA" sheetId="8" r:id="rId8"/>
-    <sheet name="NIHL" sheetId="9" r:id="rId9"/>
+    <sheet name="eForm7_PI" sheetId="10" r:id="rId2"/>
+    <sheet name="eForm6_PI" sheetId="2" r:id="rId3"/>
+    <sheet name="eForm6_Illness" sheetId="3" r:id="rId4"/>
+    <sheet name="eForm6_Mental" sheetId="4" r:id="rId5"/>
+    <sheet name="eForm6_Construction" sheetId="5" r:id="rId6"/>
+    <sheet name="eForm6_Other" sheetId="6" r:id="rId7"/>
+    <sheet name="WT" sheetId="7" r:id="rId8"/>
+    <sheet name="CAA" sheetId="8" r:id="rId9"/>
+    <sheet name="NIHL" sheetId="9" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="359">
   <si>
     <t>ReferenceNumber</t>
   </si>
@@ -929,71 +930,208 @@
     <t>85130702</t>
   </si>
   <si>
-    <t>KKFirstykfea</t>
-  </si>
-  <si>
-    <t>KKLasthmhqe</t>
-  </si>
-  <si>
-    <t>KKFirstaagvy</t>
-  </si>
-  <si>
-    <t>KKLastibnbh</t>
-  </si>
-  <si>
-    <t>KKFirstydzfj</t>
-  </si>
-  <si>
-    <t>KKLastsncde</t>
-  </si>
-  <si>
-    <t>KKFirsttkpfa</t>
-  </si>
-  <si>
-    <t>KKLastqzmvf</t>
-  </si>
-  <si>
-    <t>KKFirstagzie</t>
-  </si>
-  <si>
-    <t>KKLastoupjk</t>
-  </si>
-  <si>
-    <t>KKFirstyhaso</t>
-  </si>
-  <si>
-    <t>KKLastwtswf</t>
-  </si>
-  <si>
-    <t>KKFirstvomgb</t>
-  </si>
-  <si>
-    <t>KKLastkzqwf</t>
-  </si>
-  <si>
-    <t>KKFirsttstlf</t>
-  </si>
-  <si>
-    <t>KKLastsdstq</t>
-  </si>
-  <si>
-    <t>KKFirstykuid</t>
-  </si>
-  <si>
-    <t>KKLastmqrzh</t>
-  </si>
-  <si>
     <t>KKFirstfpuzr</t>
   </si>
   <si>
     <t>KKLastfletn</t>
+  </si>
+  <si>
+    <t>Account Number</t>
+  </si>
+  <si>
+    <t>Report Type</t>
+  </si>
+  <si>
+    <t>Injury Category</t>
+  </si>
+  <si>
+    <t>Accident Type</t>
+  </si>
+  <si>
+    <t>Described By</t>
+  </si>
+  <si>
+    <t>Mailing Address</t>
+  </si>
+  <si>
+    <t>Branch Address</t>
+  </si>
+  <si>
+    <t>Business Year</t>
+  </si>
+  <si>
+    <t>NAICS Code</t>
+  </si>
+  <si>
+    <t>Phone Number</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>Date of Birth</t>
+  </si>
+  <si>
+    <t>Language of Service</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>Job Title</t>
+  </si>
+  <si>
+    <t>Emp Start Date</t>
+  </si>
+  <si>
+    <t>Emp Years</t>
+  </si>
+  <si>
+    <t>Emp Months</t>
+  </si>
+  <si>
+    <t>Supervisor Contact</t>
+  </si>
+  <si>
+    <t># Employees</t>
+  </si>
+  <si>
+    <t>Union?</t>
+  </si>
+  <si>
+    <t>IsSpouseRelavtive</t>
+  </si>
+  <si>
+    <t>EmployerRelation</t>
+  </si>
+  <si>
+    <t>WhatHappenedInput</t>
+  </si>
+  <si>
+    <t>Injury Date</t>
+  </si>
+  <si>
+    <t>Body Parts</t>
+  </si>
+  <si>
+    <t>EmployerKnownDate</t>
+  </si>
+  <si>
+    <t>reported to?</t>
+  </si>
+  <si>
+    <t>Witness</t>
+  </si>
+  <si>
+    <t>Prior Conditions</t>
+  </si>
+  <si>
+    <t>Third Party</t>
+  </si>
+  <si>
+    <t>Objection</t>
+  </si>
+  <si>
+    <t>HealthCare</t>
+  </si>
+  <si>
+    <t>LOE</t>
+  </si>
+  <si>
+    <t>Type of Work</t>
+  </si>
+  <si>
+    <t>Wage Loss</t>
+  </si>
+  <si>
+    <t>Fainting</t>
+  </si>
+  <si>
+    <t>I work at the business</t>
+  </si>
+  <si>
+    <t>140 Erskine Avenue|Toronto|Ontario|M4P 1Z2</t>
+  </si>
+  <si>
+    <t>Employee</t>
+  </si>
+  <si>
+    <t>S First|S Last|6478787777|English</t>
+  </si>
+  <si>
+    <t>Ear(s)</t>
+  </si>
+  <si>
+    <t>Kiran|Kangula|6478777777|English</t>
+  </si>
+  <si>
+    <t>Regular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Same as mailing address </t>
+  </si>
+  <si>
+    <t>6478444444</t>
+  </si>
+  <si>
+    <t>1/Jan/2020</t>
+  </si>
+  <si>
+    <t>85266234</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>623110</t>
+  </si>
+  <si>
+    <t>KK</t>
+  </si>
+  <si>
+    <t>Kkone</t>
+  </si>
+  <si>
+    <t>1/Jan/1990</t>
+  </si>
+  <si>
+    <t>1/Feb/2025</t>
+  </si>
+  <si>
+    <t>1/Mar/2025</t>
+  </si>
+  <si>
+    <t>Yes|Clinic|1/Mar/2025|1/Mar/2025</t>
+  </si>
+  <si>
+    <t>8045 SOUTH BAY RD, SUDBURY, ON, P3E 1A1, CA</t>
+  </si>
+  <si>
+    <t>1102322</t>
+  </si>
+  <si>
+    <t>85266249</t>
+  </si>
+  <si>
+    <t>85266250</t>
+  </si>
+  <si>
+    <t>85266252</t>
+  </si>
+  <si>
+    <t>KKFirstvzakd</t>
+  </si>
+  <si>
+    <t>KKLastomhrc</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="m/mmm/yyyy"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1052,7 +1190,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1063,12 +1201,23 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
+  <dxfs count="19">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1557,13 +1706,681 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:C1">
+    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{940E15E8-DD0F-406D-92A0-8C299A35101B}">
+  <dimension ref="A1:AU2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" customWidth="true" width="22.28515625"/>
+    <col min="2" max="2" customWidth="true" width="21.42578125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="13.28515625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="11.42578125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="23.28515625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="47.42578125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="19.85546875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="22.85546875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="18.5703125"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="20.42578125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="21.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="20.85546875"/>
+    <col min="14" max="14" customWidth="true" width="30.7109375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="28.85546875"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="25.0"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="20.28515625"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="18.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="19.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="26.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="29.28515625"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="20.85546875"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="21.5703125"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="25" max="26" customWidth="true" width="19.85546875"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" width="27.28515625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="14.85546875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="16.7109375"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="15.28515625"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" width="20.5703125"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="18.5703125"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" width="14.7109375"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" width="13.42578125"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" width="10.85546875"/>
+    <col min="38" max="38" bestFit="true" customWidth="true" width="22.7109375"/>
+    <col min="39" max="39" bestFit="true" customWidth="true" width="19.85546875"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" width="13.85546875"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" width="8.5703125"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" width="12.0"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" width="20.140625"/>
+    <col min="45" max="45" customWidth="true" width="11.85546875"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" width="21.140625"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" width="21.42578125"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A1" t="s" s="0">
+        <v>221</v>
+      </c>
+      <c r="B1" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="C1" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="D1" t="s" s="0">
+        <v>223</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>224</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>225</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>226</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>228</v>
+      </c>
+      <c r="J1" t="s" s="0">
+        <v>248</v>
+      </c>
+      <c r="K1" t="s" s="0">
+        <v>229</v>
+      </c>
+      <c r="L1" t="s" s="0">
+        <v>231</v>
+      </c>
+      <c r="M1" t="s" s="0">
+        <v>232</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>234</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>236</v>
+      </c>
+      <c r="P1" t="s" s="0">
+        <v>242</v>
+      </c>
+      <c r="Q1" t="s" s="0">
+        <v>237</v>
+      </c>
+      <c r="R1" t="s" s="0">
+        <v>238</v>
+      </c>
+      <c r="S1" t="s" s="0">
+        <v>240</v>
+      </c>
+      <c r="T1" t="s" s="0">
+        <v>241</v>
+      </c>
+      <c r="U1" t="s" s="0">
+        <v>243</v>
+      </c>
+      <c r="V1" t="s" s="0">
+        <v>244</v>
+      </c>
+      <c r="W1" t="s" s="0">
+        <v>246</v>
+      </c>
+      <c r="X1" t="s" s="0">
+        <v>247</v>
+      </c>
+      <c r="Y1" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="Z1" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="AA1" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="AB1" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD1" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE1" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="AF1" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="AG1" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="AH1" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="AI1" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="AJ1" s="5" t="s">
+        <v>257</v>
+      </c>
+      <c r="AK1" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="AL1" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="AM1" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="AN1" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="AO1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="AP1" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="AQ1" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="AR1" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="AS1" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="AT1" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="AU1" s="7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:47" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>357</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>358</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>233</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="R2" t="s" s="0">
+        <v>239</v>
+      </c>
+      <c r="S2" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="U2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="V2" t="s" s="0">
+        <v>245</v>
+      </c>
+      <c r="W2" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="X2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="Y2" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="AA2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="AB2" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="AC2" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="AD2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AE2" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="AF2" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="AG2" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="AH2" t="s" s="0">
+        <v>260</v>
+      </c>
+      <c r="AI2" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="AJ2" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="AK2" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="AL2" t="s" s="0">
+        <v>253</v>
+      </c>
+      <c r="AM2" t="s" s="0">
+        <v>263</v>
+      </c>
+      <c r="AN2" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="AO2" t="s" s="0">
+        <v>264</v>
+      </c>
+      <c r="AP2" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="AQ2" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="AR2" t="s" s="0">
+        <v>268</v>
+      </c>
+      <c r="AS2" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="AT2" t="s" s="0">
+        <v>285</v>
+      </c>
+      <c r="AU2" t="s" s="0">
+        <v>286</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:XFD1">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{88CF68CF-863A-4741-8C66-57791459BD62}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB2D8E80-6FE9-41BE-8B65-712451ECD694}">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="17.7109375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="14.7109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="13.85546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="12.42578125"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="20.42578125"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="15.28515625"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="23.28515625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="13.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="11.42578125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="10.5703125"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="10.140625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="14.5703125"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="5.42578125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" width="9.42578125"/>
+    <col min="18" max="18" customWidth="true" width="29.140625"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" width="18.7109375"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="4.0"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="43.28515625"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="9.85546875"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="10.0"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" width="12.0"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" width="31.140625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" width="12.140625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="7.28515625"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="17.42578125"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="17.0"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" width="19.85546875"/>
+    <col min="32" max="32" customWidth="true" width="26.28515625"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" width="10.28515625"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" width="20.0"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" width="32.5703125"/>
+    <col min="36" max="36" bestFit="true" customWidth="true" width="8.140625"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" width="15.42578125"/>
+    <col min="38" max="38" bestFit="true" customWidth="true" width="10.5703125"/>
+    <col min="39" max="39" bestFit="true" customWidth="true" width="9.7109375"/>
+    <col min="40" max="40" customWidth="true" width="46.5703125"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" width="4.28515625"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" width="12.7109375"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" width="10.140625"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>299</v>
+      </c>
+      <c r="G1" t="s" s="0">
+        <v>300</v>
+      </c>
+      <c r="H1" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="I1" t="s" s="0">
+        <v>301</v>
+      </c>
+      <c r="J1" t="s" s="0">
+        <v>302</v>
+      </c>
+      <c r="K1" t="s" s="0">
+        <v>303</v>
+      </c>
+      <c r="L1" t="s" s="0">
+        <v>304</v>
+      </c>
+      <c r="M1" t="s" s="0">
+        <v>222</v>
+      </c>
+      <c r="N1" t="s" s="0">
+        <v>223</v>
+      </c>
+      <c r="O1" t="s" s="0">
+        <v>305</v>
+      </c>
+      <c r="P1" t="s" s="0">
+        <v>306</v>
+      </c>
+      <c r="Q1" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="R1" t="s" s="0">
+        <v>307</v>
+      </c>
+      <c r="S1" t="s" s="0">
+        <v>308</v>
+      </c>
+      <c r="T1" t="s" s="0">
+        <v>309</v>
+      </c>
+      <c r="U1" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="V1" t="s" s="0">
+        <v>310</v>
+      </c>
+      <c r="W1" t="s" s="0">
+        <v>311</v>
+      </c>
+      <c r="X1" t="s" s="0">
+        <v>312</v>
+      </c>
+      <c r="Y1" t="s" s="0">
+        <v>313</v>
+      </c>
+      <c r="Z1" t="s" s="0">
+        <v>314</v>
+      </c>
+      <c r="AA1" t="s" s="0">
+        <v>315</v>
+      </c>
+      <c r="AB1" t="s" s="0">
+        <v>316</v>
+      </c>
+      <c r="AC1" t="s" s="0">
+        <v>317</v>
+      </c>
+      <c r="AD1" t="s" s="0">
+        <v>318</v>
+      </c>
+      <c r="AE1" t="s" s="0">
+        <v>319</v>
+      </c>
+      <c r="AF1" t="s" s="0">
+        <v>320</v>
+      </c>
+      <c r="AG1" t="s" s="0">
+        <v>321</v>
+      </c>
+      <c r="AH1" t="s" s="0">
+        <v>322</v>
+      </c>
+      <c r="AI1" t="s" s="0">
+        <v>323</v>
+      </c>
+      <c r="AJ1" t="s" s="0">
+        <v>324</v>
+      </c>
+      <c r="AK1" t="s" s="0">
+        <v>325</v>
+      </c>
+      <c r="AL1" t="s" s="0">
+        <v>326</v>
+      </c>
+      <c r="AM1" t="s" s="0">
+        <v>327</v>
+      </c>
+      <c r="AN1" t="s" s="0">
+        <v>328</v>
+      </c>
+      <c r="AO1" t="s" s="0">
+        <v>329</v>
+      </c>
+      <c r="AP1" t="s" s="0">
+        <v>330</v>
+      </c>
+      <c r="AQ1" t="s" s="0">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
+      <c r="A2" t="s" s="0">
+        <v>353</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>356</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s" s="0">
+        <v>332</v>
+      </c>
+      <c r="H2" t="s" s="0">
+        <v>333</v>
+      </c>
+      <c r="I2" t="s" s="0">
+        <v>352</v>
+      </c>
+      <c r="J2" t="s" s="0">
+        <v>340</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>346</v>
+      </c>
+      <c r="N2" t="s" s="0">
+        <v>347</v>
+      </c>
+      <c r="O2" t="s" s="0">
+        <v>341</v>
+      </c>
+      <c r="P2" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="Q2" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>348</v>
+      </c>
+      <c r="S2" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="T2" t="s" s="0">
+        <v>160</v>
+      </c>
+      <c r="U2" t="s" s="0">
+        <v>334</v>
+      </c>
+      <c r="V2" t="s" s="0">
+        <v>335</v>
+      </c>
+      <c r="W2" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y2" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="Z2" t="s" s="0">
+        <v>336</v>
+      </c>
+      <c r="AA2" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="AB2" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="AC2" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="AD2" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="AE2" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="AF2" s="8" t="s">
+        <v>349</v>
+      </c>
+      <c r="AG2" t="s" s="0">
+        <v>337</v>
+      </c>
+      <c r="AH2" s="8" t="s">
+        <v>350</v>
+      </c>
+      <c r="AI2" t="s" s="0">
+        <v>338</v>
+      </c>
+      <c r="AJ2" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="AK2" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="AL2" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="AM2" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="AN2" t="s" s="0">
+        <v>351</v>
+      </c>
+      <c r="AO2" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="AP2" t="s" s="0">
+        <v>339</v>
+      </c>
+      <c r="AQ2" t="s" s="0">
+        <v>141</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A1:B1">
     <cfRule type="duplicateValues" dxfId="17" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33828E7C-EAC4-4C86-87E0-3EB8DC303443}">
   <dimension ref="A1:BY2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2124,7 +2941,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C64E6A5F-66F3-47EA-9AEB-61CD493B9923}">
   <dimension ref="A1:BW2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2670,7 +3487,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20D26FBA-7439-42B9-A201-C3C27FE83F69}">
   <dimension ref="A1:BX2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3225,7 +4042,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{047E5626-4C4D-4FFC-85FB-69A376807120}">
   <dimension ref="A1:AH2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3480,7 +4297,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{673F62D1-C22D-4ED7-B45C-1711D3211AD6}">
   <dimension ref="A1:AH2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3731,7 +4548,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0D9716D-5E3D-4891-AF91-0A6D708F5D9E}">
   <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3863,7 +4680,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B26CB9A0-785F-4428-A681-554B40CB2D7A}">
   <dimension ref="A1:W2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4041,352 +4858,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{940E15E8-DD0F-406D-92A0-8C299A35101B}">
-  <dimension ref="A1:AU2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" customWidth="true" width="22.28515625"/>
-    <col min="2" max="2" customWidth="true" width="21.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="13.28515625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="11.42578125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="23.28515625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="19.85546875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="22.85546875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="18.5703125"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="20.42578125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="21.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="20.85546875"/>
-    <col min="14" max="14" customWidth="true" width="30.7109375"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="28.85546875"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="25.0"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="20.28515625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="18.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="19.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="26.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="29.28515625"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="20.85546875"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="25" max="26" customWidth="true" width="19.85546875"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" width="27.28515625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="14.85546875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="15.28515625"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" width="20.5703125"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="18.5703125"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="14.7109375"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" width="13.42578125"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" width="10.85546875"/>
-    <col min="38" max="38" bestFit="true" customWidth="true" width="22.7109375"/>
-    <col min="39" max="39" bestFit="true" customWidth="true" width="19.85546875"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" width="13.85546875"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" width="8.5703125"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" width="12.0"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" width="20.140625"/>
-    <col min="45" max="45" customWidth="true" width="11.85546875"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" width="21.140625"/>
-    <col min="47" max="47" bestFit="true" customWidth="true" width="21.42578125"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A1" t="s" s="0">
-        <v>221</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>135</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>222</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>223</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>224</v>
-      </c>
-      <c r="F1" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>225</v>
-      </c>
-      <c r="H1" t="s" s="0">
-        <v>226</v>
-      </c>
-      <c r="I1" t="s" s="0">
-        <v>228</v>
-      </c>
-      <c r="J1" t="s" s="0">
-        <v>248</v>
-      </c>
-      <c r="K1" t="s" s="0">
-        <v>229</v>
-      </c>
-      <c r="L1" t="s" s="0">
-        <v>231</v>
-      </c>
-      <c r="M1" t="s" s="0">
-        <v>232</v>
-      </c>
-      <c r="N1" t="s" s="0">
-        <v>234</v>
-      </c>
-      <c r="O1" t="s" s="0">
-        <v>236</v>
-      </c>
-      <c r="P1" t="s" s="0">
-        <v>242</v>
-      </c>
-      <c r="Q1" t="s" s="0">
-        <v>237</v>
-      </c>
-      <c r="R1" t="s" s="0">
-        <v>238</v>
-      </c>
-      <c r="S1" t="s" s="0">
-        <v>240</v>
-      </c>
-      <c r="T1" t="s" s="0">
-        <v>241</v>
-      </c>
-      <c r="U1" t="s" s="0">
-        <v>243</v>
-      </c>
-      <c r="V1" t="s" s="0">
-        <v>244</v>
-      </c>
-      <c r="W1" t="s" s="0">
-        <v>246</v>
-      </c>
-      <c r="X1" t="s" s="0">
-        <v>247</v>
-      </c>
-      <c r="Y1" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="Z1" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="AA1" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="AB1" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="AC1" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AD1" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE1" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="AF1" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="AG1" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="AH1" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="AI1" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="AJ1" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="AK1" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="AL1" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="AM1" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="AN1" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="AO1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="AP1" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="AQ1" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="AR1" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="AS1" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="AT1" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="AU1" s="7" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="2" spans="1:47" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>312</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>313</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>80</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="H2" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="J2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="M2" t="s" s="0">
-        <v>233</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="R2" t="s" s="0">
-        <v>239</v>
-      </c>
-      <c r="S2" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="U2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="V2" t="s" s="0">
-        <v>245</v>
-      </c>
-      <c r="W2" t="s" s="0">
-        <v>141</v>
-      </c>
-      <c r="X2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="Y2" t="s" s="0">
-        <v>141</v>
-      </c>
-      <c r="Z2" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="AA2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AB2" t="s" s="0">
-        <v>43</v>
-      </c>
-      <c r="AC2" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AE2" t="s" s="0">
-        <v>141</v>
-      </c>
-      <c r="AF2" t="s" s="0">
-        <v>253</v>
-      </c>
-      <c r="AG2" t="s" s="0">
-        <v>253</v>
-      </c>
-      <c r="AH2" t="s" s="0">
-        <v>260</v>
-      </c>
-      <c r="AI2" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="AJ2" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="AK2" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="AL2" t="s" s="0">
-        <v>253</v>
-      </c>
-      <c r="AM2" t="s" s="0">
-        <v>263</v>
-      </c>
-      <c r="AN2" t="s" s="0">
-        <v>141</v>
-      </c>
-      <c r="AO2" t="s" s="0">
-        <v>264</v>
-      </c>
-      <c r="AP2" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="AQ2" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="AR2" t="s" s="0">
-        <v>268</v>
-      </c>
-      <c r="AS2" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="AT2" t="s" s="0">
-        <v>285</v>
-      </c>
-      <c r="AU2" t="s" s="0">
-        <v>286</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="A1:XFD1">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{88CF68CF-863A-4741-8C66-57791459BD62}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-</worksheet>
 </file>
--- a/src/test/resources/data/PPD/testData.xlsx
+++ b/src/test/resources/data/PPD/testData.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="363">
   <si>
     <t>ReferenceNumber</t>
   </si>
@@ -1123,6 +1123,18 @@
   </si>
   <si>
     <t>KKLastomhrc</t>
+  </si>
+  <si>
+    <t>KKFirsthnftb</t>
+  </si>
+  <si>
+    <t>KKLastaizsm</t>
+  </si>
+  <si>
+    <t>KKFirstyeuom</t>
+  </si>
+  <si>
+    <t>KKLastapheg</t>
   </si>
 </sst>
 </file>
@@ -1916,10 +1928,10 @@
         <v>287</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="F2" t="s" s="0">
         <v>80</v>

--- a/src/test/resources/data/PPD/testData.xlsx
+++ b/src/test/resources/data/PPD/testData.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="990" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="377">
   <si>
     <t>ReferenceNumber</t>
   </si>
@@ -1135,6 +1135,48 @@
   </si>
   <si>
     <t>KKLastapheg</t>
+  </si>
+  <si>
+    <t>KKFirstsletd</t>
+  </si>
+  <si>
+    <t>KKLastgksoh</t>
+  </si>
+  <si>
+    <t>KKFirstmhxjw</t>
+  </si>
+  <si>
+    <t>KKLastrkyei</t>
+  </si>
+  <si>
+    <t>KKFirstbqjad</t>
+  </si>
+  <si>
+    <t>KKLastzhhje</t>
+  </si>
+  <si>
+    <t>KKFirstevylr</t>
+  </si>
+  <si>
+    <t>KKLastpfbhm</t>
+  </si>
+  <si>
+    <t>KKFirstswzcc</t>
+  </si>
+  <si>
+    <t>KKLastjxpin</t>
+  </si>
+  <si>
+    <t>KKFirstuulak</t>
+  </si>
+  <si>
+    <t>KKLasttolrh</t>
+  </si>
+  <si>
+    <t>KKFirstwbrxs</t>
+  </si>
+  <si>
+    <t>KKLastddkdl</t>
   </si>
 </sst>
 </file>
@@ -1928,10 +1970,10 @@
         <v>287</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="F2" t="s" s="0">
         <v>80</v>

--- a/src/test/resources/data/PPD/testData.xlsx
+++ b/src/test/resources/data/PPD/testData.xlsx
@@ -3,30 +3,31 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wsib-my.sharepoint.com/personal/kiran_kangula_wsib_on_ca/Documents/Documents/Automation/DigitalClaims/src/test/resources/data/PPD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="197" documentId="14_{9D299995-2E00-4E35-9164-CFF982FDA28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{857A3A0E-2661-48E4-A152-27BA3096DFDC}"/>
+  <xr:revisionPtr revIDLastSave="219" documentId="14_{9D299995-2E00-4E35-9164-CFF982FDA28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{385E6671-B7CD-4C7F-8C92-92897DDB0ADC}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GWCC" sheetId="1" r:id="rId1"/>
     <sheet name="eForm7_PI" sheetId="10" r:id="rId2"/>
-    <sheet name="eForm6_PI" sheetId="2" r:id="rId3"/>
-    <sheet name="eForm6_Illness" sheetId="3" r:id="rId4"/>
-    <sheet name="eForm6_Mental" sheetId="4" r:id="rId5"/>
-    <sheet name="eForm6_Construction" sheetId="5" r:id="rId6"/>
-    <sheet name="eForm6_Other" sheetId="6" r:id="rId7"/>
-    <sheet name="WT" sheetId="7" r:id="rId8"/>
-    <sheet name="CAA" sheetId="8" r:id="rId9"/>
-    <sheet name="NIHL" sheetId="9" r:id="rId10"/>
+    <sheet name="B2BForm7" sheetId="11" r:id="rId3"/>
+    <sheet name="eForm6_PI" sheetId="2" r:id="rId4"/>
+    <sheet name="eForm6_Illness" sheetId="3" r:id="rId5"/>
+    <sheet name="eForm6_Mental" sheetId="4" r:id="rId6"/>
+    <sheet name="eForm6_Construction" sheetId="5" r:id="rId7"/>
+    <sheet name="eForm6_Other" sheetId="6" r:id="rId8"/>
+    <sheet name="WT" sheetId="7" r:id="rId9"/>
+    <sheet name="CAA" sheetId="8" r:id="rId10"/>
+    <sheet name="NIHL" sheetId="9" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="357">
   <si>
     <t>ReferenceNumber</t>
   </si>
@@ -930,12 +931,6 @@
     <t>85130702</t>
   </si>
   <si>
-    <t>KKFirstfpuzr</t>
-  </si>
-  <si>
-    <t>KKLastfletn</t>
-  </si>
-  <si>
     <t>Account Number</t>
   </si>
   <si>
@@ -1077,9 +1072,6 @@
     <t>1/Jan/2020</t>
   </si>
   <si>
-    <t>85266234</t>
-  </si>
-  <si>
     <t>2026</t>
   </si>
   <si>
@@ -1110,81 +1102,31 @@
     <t>1102322</t>
   </si>
   <si>
-    <t>85266249</t>
-  </si>
-  <si>
-    <t>85266250</t>
-  </si>
-  <si>
     <t>85266252</t>
   </si>
   <si>
-    <t>KKFirstvzakd</t>
-  </si>
-  <si>
-    <t>KKLastomhrc</t>
-  </si>
-  <si>
-    <t>KKFirsthnftb</t>
-  </si>
-  <si>
-    <t>KKLastaizsm</t>
-  </si>
-  <si>
-    <t>KKFirstyeuom</t>
-  </si>
-  <si>
-    <t>KKLastapheg</t>
-  </si>
-  <si>
-    <t>KKFirstsletd</t>
-  </si>
-  <si>
-    <t>KKLastgksoh</t>
-  </si>
-  <si>
-    <t>KKFirstmhxjw</t>
-  </si>
-  <si>
-    <t>KKLastrkyei</t>
-  </si>
-  <si>
-    <t>KKFirstbqjad</t>
-  </si>
-  <si>
-    <t>KKLastzhhje</t>
-  </si>
-  <si>
-    <t>KKFirstevylr</t>
-  </si>
-  <si>
-    <t>KKLastpfbhm</t>
-  </si>
-  <si>
-    <t>KKFirstswzcc</t>
-  </si>
-  <si>
-    <t>KKLastjxpin</t>
-  </si>
-  <si>
-    <t>KKFirstuulak</t>
-  </si>
-  <si>
-    <t>KKLasttolrh</t>
-  </si>
-  <si>
     <t>KKFirstwbrxs</t>
   </si>
   <si>
     <t>KKLastddkdl</t>
+  </si>
+  <si>
+    <t>accountNumber</t>
+  </si>
+  <si>
+    <t>Firstuydja</t>
+  </si>
+  <si>
+    <t>Lastxuxdu</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="m/mmm/yyyy"/>
+    <numFmt numFmtId="166" formatCode="d/mmm/yyyy"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -1244,7 +1186,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1256,6 +1198,7 @@
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1731,9 +1674,9 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="16.42578125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="11.5703125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="7.0"/>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1767,129 +1710,309 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B26CB9A0-785F-4428-A681-554B40CB2D7A}">
+  <dimension ref="A1:W2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="10.7109375" customWidth="1"/>
+    <col min="23" max="23" width="12.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G1" t="s">
+        <v>198</v>
+      </c>
+      <c r="H1" t="s">
+        <v>199</v>
+      </c>
+      <c r="I1" t="s">
+        <v>200</v>
+      </c>
+      <c r="J1" t="s">
+        <v>201</v>
+      </c>
+      <c r="K1" t="s">
+        <v>202</v>
+      </c>
+      <c r="L1" t="s">
+        <v>203</v>
+      </c>
+      <c r="M1" t="s">
+        <v>204</v>
+      </c>
+      <c r="N1" t="s">
+        <v>205</v>
+      </c>
+      <c r="O1" t="s">
+        <v>206</v>
+      </c>
+      <c r="P1" t="s">
+        <v>207</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>208</v>
+      </c>
+      <c r="R1" t="s">
+        <v>209</v>
+      </c>
+      <c r="S1" t="s">
+        <v>210</v>
+      </c>
+      <c r="T1" t="s">
+        <v>211</v>
+      </c>
+      <c r="U1" t="s">
+        <v>190</v>
+      </c>
+      <c r="V1" t="s">
+        <v>164</v>
+      </c>
+      <c r="W1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="s">
+        <v>213</v>
+      </c>
+      <c r="L2" t="s">
+        <v>214</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="P2" t="s">
+        <v>218</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>219</v>
+      </c>
+      <c r="R2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2" t="s">
+        <v>17</v>
+      </c>
+      <c r="T2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="V2" t="s">
+        <v>288</v>
+      </c>
+      <c r="W2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="U2" r:id="rId1" xr:uid="{5373313A-0822-4C8A-96F4-8E552924493A}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{940E15E8-DD0F-406D-92A0-8C299A35101B}">
   <dimension ref="A1:AU2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" width="22.28515625"/>
-    <col min="2" max="2" customWidth="true" width="21.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="13.28515625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="11.42578125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="23.28515625"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="19.85546875"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="22.85546875"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="18.5703125"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="20.42578125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="21.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="20.85546875"/>
-    <col min="14" max="14" customWidth="true" width="30.7109375"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="28.85546875"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="25.0"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="20.28515625"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="18.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="19.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="26.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="29.28515625"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="20.85546875"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="21.5703125"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="25" max="26" customWidth="true" width="19.85546875"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" width="27.28515625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="14.85546875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="15.28515625"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" width="20.5703125"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="18.5703125"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="14.7109375"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" width="13.42578125"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" width="10.85546875"/>
-    <col min="38" max="38" bestFit="true" customWidth="true" width="22.7109375"/>
-    <col min="39" max="39" bestFit="true" customWidth="true" width="19.85546875"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" width="13.85546875"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" width="8.5703125"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" width="12.0"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" width="20.140625"/>
-    <col min="45" max="45" customWidth="true" width="11.85546875"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" width="21.140625"/>
-    <col min="47" max="47" bestFit="true" customWidth="true" width="21.42578125"/>
+    <col min="1" max="1" width="22.28515625" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="30.7109375" customWidth="1"/>
+    <col min="15" max="15" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="26" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="17" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="19.85546875" customWidth="1"/>
+    <col min="27" max="27" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="16" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="12" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="11.85546875" customWidth="1"/>
+    <col min="46" max="46" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="21.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>221</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>135</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>222</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>223</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>224</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>225</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>226</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>228</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>248</v>
       </c>
-      <c r="K1" t="s" s="0">
+      <c r="K1" t="s">
         <v>229</v>
       </c>
-      <c r="L1" t="s" s="0">
+      <c r="L1" t="s">
         <v>231</v>
       </c>
-      <c r="M1" t="s" s="0">
+      <c r="M1" t="s">
         <v>232</v>
       </c>
-      <c r="N1" t="s" s="0">
+      <c r="N1" t="s">
         <v>234</v>
       </c>
-      <c r="O1" t="s" s="0">
+      <c r="O1" t="s">
         <v>236</v>
       </c>
-      <c r="P1" t="s" s="0">
+      <c r="P1" t="s">
         <v>242</v>
       </c>
-      <c r="Q1" t="s" s="0">
+      <c r="Q1" t="s">
         <v>237</v>
       </c>
-      <c r="R1" t="s" s="0">
+      <c r="R1" t="s">
         <v>238</v>
       </c>
-      <c r="S1" t="s" s="0">
+      <c r="S1" t="s">
         <v>240</v>
       </c>
-      <c r="T1" t="s" s="0">
+      <c r="T1" t="s">
         <v>241</v>
       </c>
-      <c r="U1" t="s" s="0">
+      <c r="U1" t="s">
         <v>243</v>
       </c>
-      <c r="V1" t="s" s="0">
+      <c r="V1" t="s">
         <v>244</v>
       </c>
-      <c r="W1" t="s" s="0">
+      <c r="W1" t="s">
         <v>246</v>
       </c>
-      <c r="X1" t="s" s="0">
+      <c r="X1" t="s">
         <v>247</v>
       </c>
       <c r="Y1" s="5" t="s">
@@ -1969,25 +2092,25 @@
       <c r="B2" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="C2" t="s" s="0">
-        <v>375</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>376</v>
-      </c>
-      <c r="F2" t="s" s="0">
+      <c r="C2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F2" t="s">
         <v>80</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="H2" t="s" s="0">
+      <c r="H2" t="s">
         <v>26</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="J2" t="s">
         <v>17</v>
       </c>
       <c r="K2" s="1" t="s">
@@ -1996,7 +2119,7 @@
       <c r="L2" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="M2" t="s" s="0">
+      <c r="M2" t="s">
         <v>233</v>
       </c>
       <c r="N2" s="4" t="s">
@@ -2005,13 +2128,13 @@
       <c r="O2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="P2" t="s" s="0">
+      <c r="P2" t="s">
         <v>17</v>
       </c>
       <c r="Q2" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="R2" t="s" s="0">
+      <c r="R2" t="s">
         <v>239</v>
       </c>
       <c r="S2" s="4" t="s">
@@ -2020,28 +2143,28 @@
       <c r="T2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="U2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="V2" t="s" s="0">
+      <c r="U2" t="s">
+        <v>17</v>
+      </c>
+      <c r="V2" t="s">
         <v>245</v>
       </c>
-      <c r="W2" t="s" s="0">
+      <c r="W2" t="s">
         <v>141</v>
       </c>
-      <c r="X2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="Y2" t="s" s="0">
+      <c r="X2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y2" t="s">
         <v>141</v>
       </c>
       <c r="Z2" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="AA2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AA2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB2" t="s">
         <v>43</v>
       </c>
       <c r="AC2" s="4" t="s">
@@ -2050,16 +2173,16 @@
       <c r="AD2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="AE2" t="s" s="0">
+      <c r="AE2" t="s">
         <v>141</v>
       </c>
-      <c r="AF2" t="s" s="0">
+      <c r="AF2" t="s">
         <v>253</v>
       </c>
-      <c r="AG2" t="s" s="0">
+      <c r="AG2" t="s">
         <v>253</v>
       </c>
-      <c r="AH2" t="s" s="0">
+      <c r="AH2" t="s">
         <v>260</v>
       </c>
       <c r="AI2" s="4" t="s">
@@ -2071,16 +2194,16 @@
       <c r="AK2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="AL2" t="s" s="0">
+      <c r="AL2" t="s">
         <v>253</v>
       </c>
-      <c r="AM2" t="s" s="0">
+      <c r="AM2" t="s">
         <v>263</v>
       </c>
-      <c r="AN2" t="s" s="0">
+      <c r="AN2" t="s">
         <v>141</v>
       </c>
-      <c r="AO2" t="s" s="0">
+      <c r="AO2" t="s">
         <v>264</v>
       </c>
       <c r="AP2" s="1" t="s">
@@ -2089,16 +2212,16 @@
       <c r="AQ2" s="1" t="s">
         <v>259</v>
       </c>
-      <c r="AR2" t="s" s="0">
+      <c r="AR2" t="s">
         <v>268</v>
       </c>
       <c r="AS2" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="AT2" t="s" s="0">
+      <c r="AT2" t="s">
         <v>285</v>
       </c>
-      <c r="AU2" t="s" s="0">
+      <c r="AU2" t="s">
         <v>286</v>
       </c>
     </row>
@@ -2119,310 +2242,310 @@
   <dimension ref="A1:AQ2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="16.0"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="14.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="13.85546875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="12.42578125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="20.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="15.28515625"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="23.28515625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="13.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="11.42578125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="10.5703125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="10.140625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="14.5703125"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="5.42578125"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="9.42578125"/>
-    <col min="18" max="18" customWidth="true" width="29.140625"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="18.7109375"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="4.0"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="43.28515625"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="9.85546875"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="10.0"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="12.0"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="31.140625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" width="12.140625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="7.28515625"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" width="19.85546875"/>
-    <col min="32" max="32" customWidth="true" width="26.28515625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="10.28515625"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" width="20.0"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" width="32.5703125"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" width="8.140625"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" width="15.42578125"/>
-    <col min="38" max="38" bestFit="true" customWidth="true" width="10.5703125"/>
-    <col min="39" max="39" bestFit="true" customWidth="true" width="9.7109375"/>
-    <col min="40" max="40" customWidth="true" width="46.5703125"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" width="4.28515625"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" width="12.7109375"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" width="10.140625"/>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.140625" customWidth="1"/>
+    <col min="19" max="19" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="4" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="31.140625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="26.28515625" customWidth="1"/>
+    <col min="33" max="33" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="20" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="46.5703125" customWidth="1"/>
+    <col min="41" max="41" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
         <v>297</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" t="s">
         <v>298</v>
       </c>
-      <c r="E1" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="F1" t="s" s="0">
+      <c r="H1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I1" t="s">
         <v>299</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="J1" t="s">
         <v>300</v>
       </c>
-      <c r="H1" t="s" s="0">
-        <v>84</v>
-      </c>
-      <c r="I1" t="s" s="0">
+      <c r="K1" t="s">
         <v>301</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="L1" t="s">
         <v>302</v>
       </c>
-      <c r="K1" t="s" s="0">
+      <c r="M1" t="s">
+        <v>222</v>
+      </c>
+      <c r="N1" t="s">
+        <v>223</v>
+      </c>
+      <c r="O1" t="s">
         <v>303</v>
       </c>
-      <c r="L1" t="s" s="0">
+      <c r="P1" t="s">
         <v>304</v>
       </c>
-      <c r="M1" t="s" s="0">
-        <v>222</v>
-      </c>
-      <c r="N1" t="s" s="0">
-        <v>223</v>
-      </c>
-      <c r="O1" t="s" s="0">
+      <c r="Q1" t="s">
+        <v>9</v>
+      </c>
+      <c r="R1" t="s">
         <v>305</v>
       </c>
-      <c r="P1" t="s" s="0">
+      <c r="S1" t="s">
         <v>306</v>
       </c>
-      <c r="Q1" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="R1" t="s" s="0">
+      <c r="T1" t="s">
         <v>307</v>
       </c>
-      <c r="S1" t="s" s="0">
+      <c r="U1" t="s">
+        <v>12</v>
+      </c>
+      <c r="V1" t="s">
         <v>308</v>
       </c>
-      <c r="T1" t="s" s="0">
+      <c r="W1" t="s">
         <v>309</v>
       </c>
-      <c r="U1" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="V1" t="s" s="0">
+      <c r="X1" t="s">
         <v>310</v>
       </c>
-      <c r="W1" t="s" s="0">
+      <c r="Y1" t="s">
         <v>311</v>
       </c>
-      <c r="X1" t="s" s="0">
+      <c r="Z1" t="s">
         <v>312</v>
       </c>
-      <c r="Y1" t="s" s="0">
+      <c r="AA1" t="s">
         <v>313</v>
       </c>
-      <c r="Z1" t="s" s="0">
+      <c r="AB1" t="s">
         <v>314</v>
       </c>
-      <c r="AA1" t="s" s="0">
+      <c r="AC1" t="s">
         <v>315</v>
       </c>
-      <c r="AB1" t="s" s="0">
+      <c r="AD1" t="s">
         <v>316</v>
       </c>
-      <c r="AC1" t="s" s="0">
+      <c r="AE1" t="s">
         <v>317</v>
       </c>
-      <c r="AD1" t="s" s="0">
+      <c r="AF1" t="s">
         <v>318</v>
       </c>
-      <c r="AE1" t="s" s="0">
+      <c r="AG1" t="s">
         <v>319</v>
       </c>
-      <c r="AF1" t="s" s="0">
+      <c r="AH1" t="s">
         <v>320</v>
       </c>
-      <c r="AG1" t="s" s="0">
+      <c r="AI1" t="s">
         <v>321</v>
       </c>
-      <c r="AH1" t="s" s="0">
+      <c r="AJ1" t="s">
         <v>322</v>
       </c>
-      <c r="AI1" t="s" s="0">
+      <c r="AK1" t="s">
         <v>323</v>
       </c>
-      <c r="AJ1" t="s" s="0">
+      <c r="AL1" t="s">
         <v>324</v>
       </c>
-      <c r="AK1" t="s" s="0">
+      <c r="AM1" t="s">
         <v>325</v>
       </c>
-      <c r="AL1" t="s" s="0">
+      <c r="AN1" t="s">
         <v>326</v>
       </c>
-      <c r="AM1" t="s" s="0">
+      <c r="AO1" t="s">
         <v>327</v>
       </c>
-      <c r="AN1" t="s" s="0">
+      <c r="AP1" t="s">
         <v>328</v>
       </c>
-      <c r="AO1" t="s" s="0">
+      <c r="AQ1" t="s">
         <v>329</v>
-      </c>
-      <c r="AP1" t="s" s="0">
-        <v>330</v>
-      </c>
-      <c r="AQ1" t="s" s="0">
-        <v>331</v>
       </c>
     </row>
     <row r="2" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="0">
-        <v>353</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>356</v>
-      </c>
-      <c r="C2" t="s" s="0">
+      <c r="A2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s" s="0">
+      <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" t="s" s="0">
+      <c r="G2" t="s">
+        <v>330</v>
+      </c>
+      <c r="H2" t="s">
+        <v>331</v>
+      </c>
+      <c r="I2" t="s">
+        <v>349</v>
+      </c>
+      <c r="J2" t="s">
+        <v>338</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="M2" t="s">
+        <v>343</v>
+      </c>
+      <c r="N2" t="s">
+        <v>344</v>
+      </c>
+      <c r="O2" t="s">
+        <v>339</v>
+      </c>
+      <c r="P2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>22</v>
+      </c>
+      <c r="R2" s="8" t="s">
+        <v>345</v>
+      </c>
+      <c r="S2" t="s">
+        <v>26</v>
+      </c>
+      <c r="T2" t="s">
+        <v>160</v>
+      </c>
+      <c r="U2" t="s">
         <v>332</v>
       </c>
-      <c r="H2" t="s" s="0">
+      <c r="V2" t="s">
         <v>333</v>
       </c>
-      <c r="I2" t="s" s="0">
-        <v>352</v>
-      </c>
-      <c r="J2" t="s" s="0">
+      <c r="W2" s="8" t="s">
         <v>340</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="M2" t="s" s="0">
-        <v>346</v>
-      </c>
-      <c r="N2" t="s" s="0">
-        <v>347</v>
-      </c>
-      <c r="O2" t="s" s="0">
-        <v>341</v>
-      </c>
-      <c r="P2" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="Q2" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="R2" s="8" t="s">
-        <v>348</v>
-      </c>
-      <c r="S2" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="T2" t="s" s="0">
-        <v>160</v>
-      </c>
-      <c r="U2" t="s" s="0">
-        <v>334</v>
-      </c>
-      <c r="V2" t="s" s="0">
-        <v>335</v>
-      </c>
-      <c r="W2" s="8" t="s">
-        <v>342</v>
       </c>
       <c r="X2" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="Y2" t="s" s="0">
+      <c r="Y2" t="s">
         <v>24</v>
       </c>
-      <c r="Z2" t="s" s="0">
+      <c r="Z2" t="s">
+        <v>334</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF2" s="8" t="s">
+        <v>346</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>335</v>
+      </c>
+      <c r="AH2" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="AI2" t="s">
         <v>336</v>
       </c>
-      <c r="AA2" t="s" s="0">
+      <c r="AJ2" t="s">
         <v>141</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AK2" t="s">
         <v>141</v>
       </c>
-      <c r="AC2" t="s" s="0">
+      <c r="AL2" t="s">
         <v>141</v>
       </c>
-      <c r="AD2" t="s" s="0">
-        <v>52</v>
-      </c>
-      <c r="AE2" t="s" s="0">
-        <v>43</v>
-      </c>
-      <c r="AF2" s="8" t="s">
-        <v>349</v>
-      </c>
-      <c r="AG2" t="s" s="0">
+      <c r="AM2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>348</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AP2" t="s">
         <v>337</v>
       </c>
-      <c r="AH2" s="8" t="s">
-        <v>350</v>
-      </c>
-      <c r="AI2" t="s" s="0">
-        <v>338</v>
-      </c>
-      <c r="AJ2" t="s" s="0">
-        <v>141</v>
-      </c>
-      <c r="AK2" t="s" s="0">
-        <v>141</v>
-      </c>
-      <c r="AL2" t="s" s="0">
-        <v>141</v>
-      </c>
-      <c r="AM2" t="s" s="0">
-        <v>141</v>
-      </c>
-      <c r="AN2" t="s" s="0">
-        <v>351</v>
-      </c>
-      <c r="AO2" t="s" s="0">
-        <v>141</v>
-      </c>
-      <c r="AP2" t="s" s="0">
-        <v>339</v>
-      </c>
-      <c r="AQ2" t="s" s="0">
+      <c r="AQ2" t="s">
         <v>141</v>
       </c>
     </row>
@@ -2435,80 +2558,124 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC6DEECA-BBBA-401E-A1A4-4A57DF6C3780}">
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>354</v>
+      </c>
+      <c r="B1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C1" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B2" s="9">
+        <v>32874</v>
+      </c>
+      <c r="C2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>356</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33828E7C-EAC4-4C86-87E0-3EB8DC303443}">
   <dimension ref="A1:BY2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="2" max="2" customWidth="true" width="16.42578125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="11.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="7.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="14.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="13.85546875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="13.42578125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="20.42578125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="10.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="9.7109375"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="9.42578125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="7.5703125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="14.7109375"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="10.85546875"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="14.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="22.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="8.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="18.5703125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="16.42578125"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" width="19.7109375"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="19.85546875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="19.42578125"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="23.85546875"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" width="12.85546875"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" width="19.5703125"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" width="15.140625"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" width="13.7109375"/>
-    <col min="38" max="38" bestFit="true" customWidth="true" width="16.42578125"/>
-    <col min="39" max="39" bestFit="true" customWidth="true" width="14.42578125"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" width="13.42578125"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" width="16.140625"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" width="17.28515625"/>
-    <col min="45" max="45" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" width="21.7109375"/>
-    <col min="47" max="47" bestFit="true" customWidth="true" width="12.28515625"/>
-    <col min="48" max="48" bestFit="true" customWidth="true" width="13.85546875"/>
-    <col min="49" max="49" bestFit="true" customWidth="true" width="21.42578125"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" width="17.28515625"/>
-    <col min="51" max="51" bestFit="true" customWidth="true" width="25.28515625"/>
-    <col min="52" max="54" customWidth="true" width="28.0"/>
-    <col min="55" max="55" bestFit="true" customWidth="true" width="23.5703125"/>
-    <col min="56" max="56" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="57" max="57" bestFit="true" customWidth="true" width="42.140625"/>
-    <col min="58" max="59" customWidth="true" width="33.85546875"/>
-    <col min="60" max="60" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="61" max="61" bestFit="true" customWidth="true" width="21.7109375"/>
-    <col min="62" max="62" customWidth="true" width="33.85546875"/>
-    <col min="63" max="63" bestFit="true" customWidth="true" width="10.140625"/>
-    <col min="64" max="64" customWidth="true" width="25.140625"/>
-    <col min="65" max="65" customWidth="true" width="14.7109375"/>
-    <col min="66" max="66" customWidth="true" width="20.0"/>
-    <col min="67" max="67" customWidth="true" width="33.85546875"/>
-    <col min="68" max="68" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="69" max="69" customWidth="true" width="33.85546875"/>
-    <col min="70" max="71" customWidth="true" width="23.0"/>
-    <col min="72" max="72" customWidth="true" width="18.42578125"/>
-    <col min="73" max="73" bestFit="true" customWidth="true" width="36.85546875"/>
-    <col min="74" max="75" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="76" max="78" customWidth="true" width="33.85546875"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="9" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="52" max="54" width="28" customWidth="1"/>
+    <col min="55" max="55" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="58" max="59" width="33.85546875" customWidth="1"/>
+    <col min="60" max="60" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="33.85546875" customWidth="1"/>
+    <col min="63" max="63" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="25.140625" customWidth="1"/>
+    <col min="65" max="65" width="14.7109375" customWidth="1"/>
+    <col min="66" max="66" width="20" customWidth="1"/>
+    <col min="67" max="67" width="33.85546875" customWidth="1"/>
+    <col min="68" max="68" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="33.85546875" customWidth="1"/>
+    <col min="70" max="71" width="23" customWidth="1"/>
+    <col min="72" max="72" width="18.42578125" customWidth="1"/>
+    <col min="73" max="73" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="74" max="75" width="19" bestFit="1" customWidth="1"/>
+    <col min="76" max="78" width="33.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:77" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -2748,73 +2915,73 @@
       <c r="A2" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>275</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>161</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
         <v>276</v>
       </c>
-      <c r="E2" t="s" s="0">
+      <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s" s="0">
+      <c r="F2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s" s="0">
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="I2" t="s">
         <v>160</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="J2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" t="s" s="0">
+      <c r="K2" t="s">
         <v>20</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M2" t="s" s="0">
+      <c r="M2" t="s">
         <v>22</v>
       </c>
-      <c r="N2" t="s" s="0">
+      <c r="N2" t="s">
         <v>23</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="P2" t="s" s="0">
+      <c r="P2" t="s">
         <v>26</v>
       </c>
-      <c r="Q2" t="s" s="0">
+      <c r="Q2" t="s">
         <v>160</v>
       </c>
-      <c r="R2" t="s" s="0">
+      <c r="R2" t="s">
         <v>80</v>
       </c>
-      <c r="S2" t="s" s="0">
+      <c r="S2" t="s">
         <v>27</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="U2" t="s" s="0">
+      <c r="U2" t="s">
         <v>80</v>
       </c>
-      <c r="V2" t="s" s="0">
+      <c r="V2" t="s">
         <v>43</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="X2" t="s" s="0">
+      <c r="X2" t="s">
         <v>25</v>
       </c>
       <c r="Y2" s="1" t="s">
@@ -2826,31 +2993,31 @@
       <c r="AA2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>46</v>
       </c>
-      <c r="AC2" t="s" s="0">
+      <c r="AC2" t="s">
         <v>47</v>
       </c>
       <c r="AD2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AE2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AF2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AG2" t="s" s="0">
+      <c r="AE2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG2" t="s">
         <v>49</v>
       </c>
-      <c r="AH2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AI2" t="s" s="0">
+      <c r="AH2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AI2" t="s">
         <v>52</v>
       </c>
-      <c r="AJ2" t="s" s="0">
+      <c r="AJ2" t="s">
         <v>57</v>
       </c>
       <c r="AK2" s="1" t="s">
@@ -2862,118 +3029,118 @@
       <c r="AM2" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="AN2" t="s" s="0">
+      <c r="AN2" t="s">
         <v>59</v>
       </c>
-      <c r="AO2" t="s" s="0">
+      <c r="AO2" t="s">
         <v>60</v>
       </c>
-      <c r="AP2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AQ2" t="s" s="0">
+      <c r="AP2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ2" t="s">
         <v>66</v>
       </c>
-      <c r="AR2" t="s" s="0">
+      <c r="AR2" t="s">
         <v>67</v>
       </c>
-      <c r="AS2" t="s" s="0">
+      <c r="AS2" t="s">
         <v>68</v>
       </c>
       <c r="AT2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AU2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AV2" t="s" s="0">
+      <c r="AU2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV2" t="s">
         <v>17</v>
       </c>
       <c r="AW2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AX2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AY2" t="s" s="0">
+      <c r="AX2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AY2" t="s">
         <v>76</v>
       </c>
-      <c r="AZ2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BA2" t="s" s="0">
+      <c r="AZ2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BA2" t="s">
         <v>90</v>
       </c>
-      <c r="BB2" t="s" s="0">
+      <c r="BB2" t="s">
         <v>91</v>
       </c>
-      <c r="BC2" t="s" s="0">
+      <c r="BC2" t="s">
         <v>83</v>
       </c>
-      <c r="BD2" t="s" s="0">
+      <c r="BD2" t="s">
         <v>83</v>
       </c>
-      <c r="BE2" t="s" s="0">
+      <c r="BE2" t="s">
         <v>85</v>
       </c>
-      <c r="BF2" t="s" s="0">
+      <c r="BF2" t="s">
         <v>87</v>
       </c>
-      <c r="BG2" t="s" s="0">
+      <c r="BG2" t="s">
         <v>89</v>
       </c>
-      <c r="BH2" t="s" s="0">
+      <c r="BH2" t="s">
         <v>80</v>
       </c>
-      <c r="BI2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BJ2" t="s" s="0">
+      <c r="BI2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BJ2" t="s">
         <v>83</v>
       </c>
-      <c r="BK2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BL2" t="s" s="0">
+      <c r="BK2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BL2" t="s">
         <v>83</v>
       </c>
-      <c r="BM2" t="s" s="0">
+      <c r="BM2" t="s">
         <v>99</v>
       </c>
-      <c r="BN2" t="s" s="0">
+      <c r="BN2" t="s">
         <v>100</v>
       </c>
-      <c r="BO2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BP2" t="s" s="0">
+      <c r="BO2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BP2" t="s">
         <v>83</v>
       </c>
-      <c r="BQ2" t="s" s="0">
+      <c r="BQ2" t="s">
         <v>105</v>
       </c>
-      <c r="BR2" t="s" s="0">
+      <c r="BR2" t="s">
         <v>106</v>
       </c>
-      <c r="BS2" t="s" s="0">
+      <c r="BS2" t="s">
         <v>108</v>
       </c>
-      <c r="BT2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BU2" t="s" s="0">
+      <c r="BT2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BU2" t="s">
         <v>110</v>
       </c>
-      <c r="BV2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BW2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BX2" t="s" s="0">
+      <c r="BV2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BX2" t="s">
         <v>114</v>
       </c>
-      <c r="BY2" t="s" s="0">
+      <c r="BY2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2995,79 +3162,79 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C64E6A5F-66F3-47EA-9AEB-61CD493B9923}">
   <dimension ref="A1:BW2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="13.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="4.140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="14.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="33.85546875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="13.42578125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="20.42578125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="10.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="9.7109375"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="9.42578125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="7.5703125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="14.7109375"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="10.85546875"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="14.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="22.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="8.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="18.5703125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="16.42578125"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" width="19.7109375"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="19.85546875"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="19.42578125"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="23.85546875"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" width="12.85546875"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" width="19.5703125"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" width="15.140625"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" width="19.85546875"/>
-    <col min="38" max="38" customWidth="true" width="19.85546875"/>
-    <col min="39" max="39" bestFit="true" customWidth="true" width="15.140625"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" width="16.140625"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" width="17.28515625"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" width="21.7109375"/>
-    <col min="45" max="45" bestFit="true" customWidth="true" width="12.28515625"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" width="13.85546875"/>
-    <col min="47" max="47" bestFit="true" customWidth="true" width="21.42578125"/>
-    <col min="48" max="48" bestFit="true" customWidth="true" width="17.28515625"/>
-    <col min="49" max="49" bestFit="true" customWidth="true" width="25.28515625"/>
-    <col min="50" max="52" customWidth="true" width="28.0"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" width="23.5703125"/>
-    <col min="54" max="54" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="55" max="55" bestFit="true" customWidth="true" width="42.140625"/>
-    <col min="56" max="57" customWidth="true" width="33.85546875"/>
-    <col min="58" max="58" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="59" max="59" bestFit="true" customWidth="true" width="21.7109375"/>
-    <col min="60" max="60" customWidth="true" width="33.85546875"/>
-    <col min="61" max="61" bestFit="true" customWidth="true" width="10.140625"/>
-    <col min="62" max="62" customWidth="true" width="25.140625"/>
-    <col min="63" max="63" customWidth="true" width="14.7109375"/>
-    <col min="64" max="64" customWidth="true" width="20.0"/>
-    <col min="65" max="65" customWidth="true" width="33.85546875"/>
-    <col min="66" max="66" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="67" max="67" customWidth="true" width="33.85546875"/>
-    <col min="68" max="69" customWidth="true" width="23.0"/>
-    <col min="70" max="70" customWidth="true" width="18.42578125"/>
-    <col min="71" max="71" bestFit="true" customWidth="true" width="36.85546875"/>
-    <col min="72" max="73" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="74" max="76" customWidth="true" width="33.85546875"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="8" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="19.85546875" customWidth="1"/>
+    <col min="39" max="39" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="50" max="52" width="28" customWidth="1"/>
+    <col min="53" max="53" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="56" max="57" width="33.85546875" customWidth="1"/>
+    <col min="58" max="58" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="33.85546875" customWidth="1"/>
+    <col min="61" max="61" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="25.140625" customWidth="1"/>
+    <col min="63" max="63" width="14.7109375" customWidth="1"/>
+    <col min="64" max="64" width="20" customWidth="1"/>
+    <col min="65" max="65" width="33.85546875" customWidth="1"/>
+    <col min="66" max="66" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="33.85546875" customWidth="1"/>
+    <col min="68" max="69" width="23" customWidth="1"/>
+    <col min="70" max="70" width="18.42578125" customWidth="1"/>
+    <col min="71" max="71" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="72" max="73" width="19" bestFit="1" customWidth="1"/>
+    <col min="74" max="76" width="33.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:75" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3298,76 +3465,76 @@
       </c>
     </row>
     <row r="2" spans="1:75" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>291</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>277</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>161</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
         <v>278</v>
       </c>
-      <c r="E2" t="s" s="0">
+      <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s" s="0">
+      <c r="F2" t="s">
         <v>119</v>
       </c>
-      <c r="G2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s" s="0">
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="I2" t="s">
         <v>160</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="J2" t="s">
         <v>19</v>
       </c>
-      <c r="K2" t="s" s="0">
+      <c r="K2" t="s">
         <v>20</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M2" t="s" s="0">
+      <c r="M2" t="s">
         <v>22</v>
       </c>
-      <c r="N2" t="s" s="0">
+      <c r="N2" t="s">
         <v>23</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="P2" t="s" s="0">
+      <c r="P2" t="s">
         <v>26</v>
       </c>
-      <c r="Q2" t="s" s="0">
+      <c r="Q2" t="s">
         <v>160</v>
       </c>
-      <c r="R2" t="s" s="0">
+      <c r="R2" t="s">
         <v>80</v>
       </c>
-      <c r="S2" t="s" s="0">
+      <c r="S2" t="s">
         <v>27</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="U2" t="s" s="0">
+      <c r="U2" t="s">
         <v>80</v>
       </c>
-      <c r="V2" t="s" s="0">
+      <c r="V2" t="s">
         <v>43</v>
       </c>
       <c r="W2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="X2" t="s" s="0">
+      <c r="X2" t="s">
         <v>25</v>
       </c>
       <c r="Y2" s="1" t="s">
@@ -3379,148 +3546,148 @@
       <c r="AA2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>46</v>
       </c>
-      <c r="AC2" t="s" s="0">
+      <c r="AC2" t="s">
         <v>47</v>
       </c>
       <c r="AD2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AE2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AF2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AG2" t="s" s="0">
+      <c r="AE2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG2" t="s">
         <v>49</v>
       </c>
-      <c r="AH2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AI2" t="s" s="0">
+      <c r="AH2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AI2" t="s">
         <v>52</v>
       </c>
-      <c r="AJ2" t="s" s="0">
+      <c r="AJ2" t="s">
         <v>57</v>
       </c>
-      <c r="AK2" t="s" s="0">
+      <c r="AK2" t="s">
         <v>123</v>
       </c>
-      <c r="AL2" t="s" s="0">
+      <c r="AL2" t="s">
         <v>124</v>
       </c>
       <c r="AM2" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="AN2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AO2" t="s" s="0">
+      <c r="AN2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO2" t="s">
         <v>66</v>
       </c>
-      <c r="AP2" t="s" s="0">
+      <c r="AP2" t="s">
         <v>67</v>
       </c>
-      <c r="AQ2" t="s" s="0">
+      <c r="AQ2" t="s">
         <v>68</v>
       </c>
       <c r="AR2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AS2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AT2" t="s" s="0">
+      <c r="AS2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AT2" t="s">
         <v>17</v>
       </c>
       <c r="AU2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AV2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AW2" t="s" s="0">
+      <c r="AV2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AW2" t="s">
         <v>76</v>
       </c>
-      <c r="AX2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AY2" t="s" s="0">
+      <c r="AX2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AY2" t="s">
         <v>90</v>
       </c>
-      <c r="AZ2" t="s" s="0">
+      <c r="AZ2" t="s">
         <v>91</v>
       </c>
-      <c r="BA2" t="s" s="0">
+      <c r="BA2" t="s">
         <v>83</v>
       </c>
-      <c r="BB2" t="s" s="0">
+      <c r="BB2" t="s">
         <v>83</v>
       </c>
-      <c r="BC2" t="s" s="0">
+      <c r="BC2" t="s">
         <v>85</v>
       </c>
-      <c r="BD2" t="s" s="0">
+      <c r="BD2" t="s">
         <v>87</v>
       </c>
-      <c r="BE2" t="s" s="0">
+      <c r="BE2" t="s">
         <v>89</v>
       </c>
-      <c r="BF2" t="s" s="0">
+      <c r="BF2" t="s">
         <v>80</v>
       </c>
-      <c r="BG2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BH2" t="s" s="0">
+      <c r="BG2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BH2" t="s">
         <v>83</v>
       </c>
-      <c r="BI2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BJ2" t="s" s="0">
+      <c r="BI2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BJ2" t="s">
         <v>83</v>
       </c>
-      <c r="BK2" t="s" s="0">
+      <c r="BK2" t="s">
         <v>99</v>
       </c>
-      <c r="BL2" t="s" s="0">
+      <c r="BL2" t="s">
         <v>100</v>
       </c>
-      <c r="BM2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BN2" t="s" s="0">
+      <c r="BM2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BN2" t="s">
         <v>83</v>
       </c>
-      <c r="BO2" t="s" s="0">
+      <c r="BO2" t="s">
         <v>105</v>
       </c>
-      <c r="BP2" t="s" s="0">
+      <c r="BP2" t="s">
         <v>106</v>
       </c>
-      <c r="BQ2" t="s" s="0">
+      <c r="BQ2" t="s">
         <v>108</v>
       </c>
-      <c r="BR2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BS2" t="s" s="0">
+      <c r="BR2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BS2" t="s">
         <v>110</v>
       </c>
-      <c r="BT2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BU2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BV2" t="s" s="0">
+      <c r="BT2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BV2" t="s">
         <v>114</v>
       </c>
-      <c r="BW2" t="s" s="0">
+      <c r="BW2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3541,79 +3708,79 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20D26FBA-7439-42B9-A201-C3C27FE83F69}">
   <dimension ref="A1:BX2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="13.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="4.140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="14.7109375"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="24.28515625"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="20.42578125"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="10.140625"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="9.7109375"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="9.42578125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="7.5703125"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="14.7109375"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="10.85546875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="14.85546875"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="22.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="8.0"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" width="18.5703125"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="16.42578125"/>
-    <col min="25" max="25" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="19.7109375"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" width="19.85546875"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="19.42578125"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="23.85546875"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="12.85546875"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" width="19.5703125"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" width="17.28515625"/>
-    <col min="36" max="36" bestFit="true" customWidth="true" width="15.140625"/>
-    <col min="37" max="38" customWidth="true" width="15.140625"/>
-    <col min="39" max="39" bestFit="true" customWidth="true" width="13.42578125"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" width="9.0"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" width="16.140625"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" width="17.28515625"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="45" max="45" bestFit="true" customWidth="true" width="21.7109375"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" width="12.28515625"/>
-    <col min="47" max="47" bestFit="true" customWidth="true" width="13.85546875"/>
-    <col min="48" max="48" bestFit="true" customWidth="true" width="21.42578125"/>
-    <col min="49" max="49" bestFit="true" customWidth="true" width="17.28515625"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" width="25.28515625"/>
-    <col min="51" max="53" customWidth="true" width="28.0"/>
-    <col min="54" max="54" bestFit="true" customWidth="true" width="23.5703125"/>
-    <col min="55" max="55" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="56" max="56" bestFit="true" customWidth="true" width="42.140625"/>
-    <col min="57" max="58" customWidth="true" width="33.85546875"/>
-    <col min="59" max="59" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="60" max="60" bestFit="true" customWidth="true" width="21.7109375"/>
-    <col min="61" max="61" customWidth="true" width="33.85546875"/>
-    <col min="62" max="62" bestFit="true" customWidth="true" width="10.140625"/>
-    <col min="63" max="63" customWidth="true" width="25.140625"/>
-    <col min="64" max="64" customWidth="true" width="14.7109375"/>
-    <col min="65" max="65" customWidth="true" width="20.0"/>
-    <col min="66" max="66" customWidth="true" width="33.85546875"/>
-    <col min="67" max="67" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="68" max="68" customWidth="true" width="33.85546875"/>
-    <col min="69" max="70" customWidth="true" width="23.0"/>
-    <col min="71" max="71" customWidth="true" width="18.42578125"/>
-    <col min="72" max="72" bestFit="true" customWidth="true" width="36.85546875"/>
-    <col min="73" max="74" bestFit="true" customWidth="true" width="19.0"/>
-    <col min="75" max="77" customWidth="true" width="33.85546875"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="15.140625" customWidth="1"/>
+    <col min="39" max="39" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="9" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="51" max="53" width="28" customWidth="1"/>
+    <col min="54" max="54" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="57" max="58" width="33.85546875" customWidth="1"/>
+    <col min="59" max="59" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="33.85546875" customWidth="1"/>
+    <col min="62" max="62" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="25.140625" customWidth="1"/>
+    <col min="64" max="64" width="14.7109375" customWidth="1"/>
+    <col min="65" max="65" width="20" customWidth="1"/>
+    <col min="66" max="66" width="33.85546875" customWidth="1"/>
+    <col min="67" max="67" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="33.85546875" customWidth="1"/>
+    <col min="69" max="70" width="23" customWidth="1"/>
+    <col min="71" max="71" width="18.42578125" customWidth="1"/>
+    <col min="72" max="72" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="73" max="74" width="19" bestFit="1" customWidth="1"/>
+    <col min="75" max="77" width="33.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:76" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -3847,73 +4014,73 @@
       </c>
     </row>
     <row r="2" spans="1:76" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>292</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>279</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>161</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
         <v>280</v>
       </c>
-      <c r="E2" t="s" s="0">
+      <c r="E2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s" s="0">
+      <c r="F2" t="s">
         <v>126</v>
       </c>
-      <c r="G2" t="s" s="0">
+      <c r="G2" t="s">
         <v>127</v>
       </c>
-      <c r="H2" t="s" s="0">
+      <c r="H2" t="s">
         <v>160</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="I2" t="s">
         <v>19</v>
       </c>
-      <c r="J2" t="s" s="0">
+      <c r="J2" t="s">
         <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>22</v>
       </c>
-      <c r="M2" t="s" s="0">
+      <c r="M2" t="s">
         <v>23</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="O2" t="s" s="0">
+      <c r="O2" t="s">
         <v>26</v>
       </c>
-      <c r="P2" t="s" s="0">
+      <c r="P2" t="s">
         <v>160</v>
       </c>
-      <c r="Q2" t="s" s="0">
+      <c r="Q2" t="s">
         <v>80</v>
       </c>
-      <c r="R2" t="s" s="0">
+      <c r="R2" t="s">
         <v>27</v>
       </c>
       <c r="S2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="T2" t="s" s="0">
+      <c r="T2" t="s">
         <v>80</v>
       </c>
-      <c r="U2" t="s" s="0">
+      <c r="U2" t="s">
         <v>43</v>
       </c>
       <c r="V2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="W2" t="s" s="0">
+      <c r="W2" t="s">
         <v>25</v>
       </c>
       <c r="X2" s="1" t="s">
@@ -3925,31 +4092,31 @@
       <c r="Z2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="AA2" t="s" s="0">
+      <c r="AA2" t="s">
         <v>46</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>47</v>
       </c>
       <c r="AC2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AD2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AE2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AF2" t="s" s="0">
+      <c r="AD2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF2" t="s">
         <v>49</v>
       </c>
-      <c r="AG2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AH2" t="s" s="0">
+      <c r="AG2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH2" t="s">
         <v>52</v>
       </c>
-      <c r="AI2" t="s" s="0">
+      <c r="AI2" t="s">
         <v>57</v>
       </c>
       <c r="AJ2" s="1" t="s">
@@ -3961,118 +4128,118 @@
       <c r="AL2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="AM2" t="s" s="0">
+      <c r="AM2" t="s">
         <v>59</v>
       </c>
-      <c r="AN2" t="s" s="0">
+      <c r="AN2" t="s">
         <v>60</v>
       </c>
-      <c r="AO2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AP2" t="s" s="0">
+      <c r="AO2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP2" t="s">
         <v>66</v>
       </c>
-      <c r="AQ2" t="s" s="0">
+      <c r="AQ2" t="s">
         <v>67</v>
       </c>
-      <c r="AR2" t="s" s="0">
+      <c r="AR2" t="s">
         <v>68</v>
       </c>
       <c r="AS2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AT2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AU2" t="s" s="0">
+      <c r="AT2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU2" t="s">
         <v>17</v>
       </c>
       <c r="AV2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="AW2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AX2" t="s" s="0">
+      <c r="AW2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AX2" t="s">
         <v>76</v>
       </c>
-      <c r="AY2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="AZ2" t="s" s="0">
+      <c r="AY2" t="s">
+        <v>17</v>
+      </c>
+      <c r="AZ2" t="s">
         <v>90</v>
       </c>
-      <c r="BA2" t="s" s="0">
+      <c r="BA2" t="s">
         <v>91</v>
       </c>
-      <c r="BB2" t="s" s="0">
+      <c r="BB2" t="s">
         <v>83</v>
       </c>
-      <c r="BC2" t="s" s="0">
+      <c r="BC2" t="s">
         <v>83</v>
       </c>
-      <c r="BD2" t="s" s="0">
+      <c r="BD2" t="s">
         <v>85</v>
       </c>
-      <c r="BE2" t="s" s="0">
+      <c r="BE2" t="s">
         <v>87</v>
       </c>
-      <c r="BF2" t="s" s="0">
+      <c r="BF2" t="s">
         <v>89</v>
       </c>
-      <c r="BG2" t="s" s="0">
+      <c r="BG2" t="s">
         <v>80</v>
       </c>
-      <c r="BH2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BI2" t="s" s="0">
+      <c r="BH2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BI2" t="s">
         <v>83</v>
       </c>
-      <c r="BJ2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BK2" t="s" s="0">
+      <c r="BJ2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BK2" t="s">
         <v>83</v>
       </c>
-      <c r="BL2" t="s" s="0">
+      <c r="BL2" t="s">
         <v>99</v>
       </c>
-      <c r="BM2" t="s" s="0">
+      <c r="BM2" t="s">
         <v>100</v>
       </c>
-      <c r="BN2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BO2" t="s" s="0">
+      <c r="BN2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BO2" t="s">
         <v>83</v>
       </c>
-      <c r="BP2" t="s" s="0">
+      <c r="BP2" t="s">
         <v>105</v>
       </c>
-      <c r="BQ2" t="s" s="0">
+      <c r="BQ2" t="s">
         <v>106</v>
       </c>
-      <c r="BR2" t="s" s="0">
+      <c r="BR2" t="s">
         <v>108</v>
       </c>
-      <c r="BS2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BT2" t="s" s="0">
+      <c r="BS2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BT2" t="s">
         <v>110</v>
       </c>
-      <c r="BU2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BV2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="BW2" t="s" s="0">
+      <c r="BU2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>17</v>
+      </c>
+      <c r="BW2" t="s">
         <v>114</v>
       </c>
-      <c r="BX2" t="s" s="0">
+      <c r="BX2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -4096,39 +4263,39 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{047E5626-4C4D-4FFC-85FB-69A376807120}">
   <dimension ref="A1:AH2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="13.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="4.140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="23.28515625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="10.140625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="9.7109375"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="9.42578125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="7.5703125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="14.7109375"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="14.85546875"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="22.85546875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="8.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="12.85546875"/>
-    <col min="22" max="23" customWidth="true" width="18.42578125"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="19.5703125"/>
-    <col min="27" max="29" customWidth="true" width="19.5703125"/>
-    <col min="30" max="32" customWidth="true" width="17.28515625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="19.85546875"/>
-    <col min="34" max="35" customWidth="true" width="33.85546875"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="18.42578125" customWidth="1"/>
+    <col min="24" max="24" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="19.5703125" customWidth="1"/>
+    <col min="30" max="32" width="17.28515625" customWidth="1"/>
+    <col min="33" max="33" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="33.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4236,58 +4403,58 @@
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>293</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>281</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>161</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
         <v>282</v>
       </c>
-      <c r="E2" t="s" s="0">
+      <c r="E2" t="s">
         <v>133</v>
       </c>
-      <c r="F2" t="s" s="0">
+      <c r="F2" t="s">
         <v>141</v>
       </c>
-      <c r="G2" t="s" s="0">
+      <c r="G2" t="s">
         <v>134</v>
       </c>
-      <c r="H2" t="s" s="0">
+      <c r="H2" t="s">
         <v>19</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="I2" t="s">
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K2" t="s" s="0">
+      <c r="K2" t="s">
         <v>22</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>23</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="N2" t="s" s="0">
+      <c r="N2" t="s">
         <v>80</v>
       </c>
-      <c r="O2" t="s" s="0">
+      <c r="O2" t="s">
         <v>27</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" t="s" s="0">
+      <c r="Q2" t="s">
         <v>80</v>
       </c>
-      <c r="R2" t="s" s="0">
+      <c r="R2" t="s">
         <v>43</v>
       </c>
       <c r="S2" s="1" t="s">
@@ -4296,46 +4463,46 @@
       <c r="T2" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="U2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="V2" t="s" s="0">
+      <c r="U2" t="s">
+        <v>17</v>
+      </c>
+      <c r="V2" t="s">
         <v>141</v>
       </c>
-      <c r="W2" t="s" s="0">
+      <c r="W2" t="s">
         <v>141</v>
       </c>
-      <c r="X2" t="s" s="0">
+      <c r="X2" t="s">
         <v>49</v>
       </c>
-      <c r="Y2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="Z2" t="s" s="0">
+      <c r="Y2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z2" t="s">
         <v>52</v>
       </c>
-      <c r="AA2" t="s" s="0">
+      <c r="AA2" t="s">
         <v>143</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>83</v>
       </c>
-      <c r="AC2" t="s" s="0">
+      <c r="AC2" t="s">
         <v>145</v>
       </c>
-      <c r="AD2" t="s" s="0">
+      <c r="AD2" t="s">
         <v>43</v>
       </c>
-      <c r="AE2" t="s" s="0">
+      <c r="AE2" t="s">
         <v>148</v>
       </c>
-      <c r="AF2" t="s" s="0">
+      <c r="AF2" t="s">
         <v>150</v>
       </c>
-      <c r="AG2" t="s" s="0">
+      <c r="AG2" t="s">
         <v>43</v>
       </c>
-      <c r="AH2" t="s" s="0">
+      <c r="AH2" t="s">
         <v>114</v>
       </c>
     </row>
@@ -4351,39 +4518,39 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{673F62D1-C22D-4ED7-B45C-1711D3211AD6}">
   <dimension ref="A1:AH2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="17.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="13.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="4.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="4.140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="17.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="23.28515625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="10.140625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="9.7109375"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="9.42578125"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="7.5703125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="14.7109375"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="14.85546875"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="22.85546875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="47.42578125"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="8.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="12.85546875"/>
-    <col min="22" max="23" customWidth="true" width="18.42578125"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" width="17.42578125"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" width="19.5703125"/>
-    <col min="27" max="29" customWidth="true" width="19.5703125"/>
-    <col min="30" max="32" customWidth="true" width="17.28515625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" width="19.85546875"/>
-    <col min="34" max="35" customWidth="true" width="33.85546875"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="18.42578125" customWidth="1"/>
+    <col min="24" max="24" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="19.5703125" customWidth="1"/>
+    <col min="30" max="32" width="17.28515625" customWidth="1"/>
+    <col min="33" max="33" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="33.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4491,58 +4658,58 @@
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.25">
-      <c r="A2" t="s" s="0">
+      <c r="A2" t="s">
         <v>289</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>283</v>
       </c>
-      <c r="C2" t="s" s="0">
+      <c r="C2" t="s">
         <v>161</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
         <v>284</v>
       </c>
-      <c r="E2" t="s" s="0">
+      <c r="E2" t="s">
         <v>133</v>
       </c>
-      <c r="F2" t="s" s="0">
+      <c r="F2" t="s">
         <v>141</v>
       </c>
-      <c r="G2" t="s" s="0">
+      <c r="G2" t="s">
         <v>156</v>
       </c>
-      <c r="H2" t="s" s="0">
+      <c r="H2" t="s">
         <v>19</v>
       </c>
-      <c r="I2" t="s" s="0">
+      <c r="I2" t="s">
         <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K2" t="s" s="0">
+      <c r="K2" t="s">
         <v>22</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>23</v>
       </c>
       <c r="M2" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="N2" t="s" s="0">
+      <c r="N2" t="s">
         <v>80</v>
       </c>
-      <c r="O2" t="s" s="0">
+      <c r="O2" t="s">
         <v>27</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="Q2" t="s" s="0">
+      <c r="Q2" t="s">
         <v>80</v>
       </c>
-      <c r="R2" t="s" s="0">
+      <c r="R2" t="s">
         <v>43</v>
       </c>
       <c r="S2" s="1" t="s">
@@ -4551,46 +4718,46 @@
       <c r="T2" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="U2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="V2" t="s" s="0">
+      <c r="U2" t="s">
+        <v>17</v>
+      </c>
+      <c r="V2" t="s">
         <v>141</v>
       </c>
-      <c r="W2" t="s" s="0">
+      <c r="W2" t="s">
         <v>141</v>
       </c>
-      <c r="X2" t="s" s="0">
+      <c r="X2" t="s">
         <v>49</v>
       </c>
-      <c r="Y2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="Z2" t="s" s="0">
+      <c r="Y2" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z2" t="s">
         <v>52</v>
       </c>
-      <c r="AA2" t="s" s="0">
+      <c r="AA2" t="s">
         <v>143</v>
       </c>
-      <c r="AB2" t="s" s="0">
+      <c r="AB2" t="s">
         <v>83</v>
       </c>
-      <c r="AC2" t="s" s="0">
+      <c r="AC2" t="s">
         <v>145</v>
       </c>
-      <c r="AD2" t="s" s="0">
+      <c r="AD2" t="s">
         <v>43</v>
       </c>
-      <c r="AE2" t="s" s="0">
+      <c r="AE2" t="s">
         <v>148</v>
       </c>
-      <c r="AF2" t="s" s="0">
+      <c r="AF2" t="s">
         <v>150</v>
       </c>
-      <c r="AG2" t="s" s="0">
+      <c r="AG2" t="s">
         <v>43</v>
       </c>
-      <c r="AH2" t="s" s="0">
+      <c r="AH2" t="s">
         <v>114</v>
       </c>
     </row>
@@ -4602,79 +4769,79 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0D9716D-5E3D-4891-AF91-0A6D708F5D9E}">
   <dimension ref="A1:R2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="13.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="11.140625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="15.5703125"/>
-    <col min="5" max="10" customWidth="true" width="11.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="28.85546875"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="18.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="24.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="21.0"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="19.28515625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="25.28515625"/>
-    <col min="17" max="17" customWidth="true" width="10.7109375"/>
-    <col min="18" max="18" customWidth="true" width="12.42578125"/>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="11.140625" customWidth="1"/>
+    <col min="11" max="11" width="28.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" customWidth="1"/>
+    <col min="18" max="18" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" t="s" s="0">
+      <c r="A1" t="s">
         <v>157</v>
       </c>
-      <c r="B1" t="s" s="0">
+      <c r="B1" t="s">
         <v>162</v>
       </c>
-      <c r="C1" t="s" s="0">
+      <c r="C1" t="s">
         <v>163</v>
       </c>
-      <c r="D1" t="s" s="0">
+      <c r="D1" t="s">
         <v>166</v>
       </c>
-      <c r="E1" t="s" s="0">
+      <c r="E1" t="s">
         <v>171</v>
       </c>
-      <c r="F1" t="s" s="0">
+      <c r="F1" t="s">
         <v>172</v>
       </c>
-      <c r="G1" t="s" s="0">
+      <c r="G1" t="s">
         <v>173</v>
       </c>
-      <c r="H1" t="s" s="0">
+      <c r="H1" t="s">
         <v>174</v>
       </c>
-      <c r="I1" t="s" s="0">
+      <c r="I1" t="s">
         <v>175</v>
       </c>
-      <c r="J1" t="s" s="0">
+      <c r="J1" t="s">
         <v>176</v>
       </c>
-      <c r="K1" t="s" s="0">
+      <c r="K1" t="s">
         <v>180</v>
       </c>
-      <c r="L1" t="s" s="0">
+      <c r="L1" t="s">
         <v>182</v>
       </c>
-      <c r="M1" t="s" s="0">
+      <c r="M1" t="s">
         <v>183</v>
       </c>
-      <c r="N1" t="s" s="0">
+      <c r="N1" t="s">
         <v>184</v>
       </c>
-      <c r="O1" t="s" s="0">
+      <c r="O1" t="s">
         <v>185</v>
       </c>
-      <c r="P1" t="s" s="0">
+      <c r="P1" t="s">
         <v>190</v>
       </c>
-      <c r="Q1" t="s" s="0">
+      <c r="Q1" t="s">
         <v>164</v>
       </c>
-      <c r="R1" t="s" s="0">
+      <c r="R1" t="s">
         <v>165</v>
       </c>
     </row>
@@ -4682,46 +4849,46 @@
       <c r="A2" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B2" t="s" s="0">
+      <c r="B2" t="s">
         <v>169</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="D2" t="s" s="0">
+      <c r="D2" t="s">
         <v>167</v>
       </c>
-      <c r="E2" t="s" s="0">
+      <c r="E2" t="s">
         <v>177</v>
       </c>
-      <c r="F2" t="s" s="0">
+      <c r="F2" t="s">
         <v>178</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="K2" t="s" s="0">
+      <c r="K2" t="s">
         <v>181</v>
       </c>
-      <c r="L2" t="s" s="0">
+      <c r="L2" t="s">
         <v>186</v>
       </c>
-      <c r="M2" t="s" s="0">
+      <c r="M2" t="s">
         <v>187</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="O2" t="s" s="0">
+      <c r="O2" t="s">
         <v>189</v>
       </c>
       <c r="P2" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="Q2" t="s" s="0">
+      <c r="Q2" t="s">
         <v>192</v>
       </c>
-      <c r="R2" t="s" s="0">
+      <c r="R2" t="s">
         <v>193</v>
       </c>
     </row>
@@ -4732,184 +4899,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B26CB9A0-785F-4428-A681-554B40CB2D7A}">
-  <dimension ref="A1:W2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="13.85546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="12.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="11.140625"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="13.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="7.5703125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="10.85546875"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="18.42578125"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="11.28515625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="18.0"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="24.140625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="20.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" width="12.28515625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" width="10.7109375"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" width="12.28515625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" width="13.28515625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="10.85546875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" width="12.7109375"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="12.140625"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" width="10.5703125"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="16.7109375"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="25.28515625"/>
-    <col min="22" max="22" customWidth="true" width="10.7109375"/>
-    <col min="23" max="23" customWidth="true" width="12.42578125"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" t="s" s="0">
-        <v>157</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>162</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>163</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>194</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>196</v>
-      </c>
-      <c r="F1" t="s" s="0">
-        <v>197</v>
-      </c>
-      <c r="G1" t="s" s="0">
-        <v>198</v>
-      </c>
-      <c r="H1" t="s" s="0">
-        <v>199</v>
-      </c>
-      <c r="I1" t="s" s="0">
-        <v>200</v>
-      </c>
-      <c r="J1" t="s" s="0">
-        <v>201</v>
-      </c>
-      <c r="K1" t="s" s="0">
-        <v>202</v>
-      </c>
-      <c r="L1" t="s" s="0">
-        <v>203</v>
-      </c>
-      <c r="M1" t="s" s="0">
-        <v>204</v>
-      </c>
-      <c r="N1" t="s" s="0">
-        <v>205</v>
-      </c>
-      <c r="O1" t="s" s="0">
-        <v>206</v>
-      </c>
-      <c r="P1" t="s" s="0">
-        <v>207</v>
-      </c>
-      <c r="Q1" t="s" s="0">
-        <v>208</v>
-      </c>
-      <c r="R1" t="s" s="0">
-        <v>209</v>
-      </c>
-      <c r="S1" t="s" s="0">
-        <v>210</v>
-      </c>
-      <c r="T1" t="s" s="0">
-        <v>211</v>
-      </c>
-      <c r="U1" t="s" s="0">
-        <v>190</v>
-      </c>
-      <c r="V1" t="s" s="0">
-        <v>164</v>
-      </c>
-      <c r="W1" t="s" s="0">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>169</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="E2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="H2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="I2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="J2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="K2" t="s" s="0">
-        <v>213</v>
-      </c>
-      <c r="L2" t="s" s="0">
-        <v>214</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="P2" t="s" s="0">
-        <v>218</v>
-      </c>
-      <c r="Q2" t="s" s="0">
-        <v>219</v>
-      </c>
-      <c r="R2" t="s" s="0">
-        <v>43</v>
-      </c>
-      <c r="S2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="T2" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="V2" t="s" s="0">
-        <v>288</v>
-      </c>
-      <c r="W2" t="s" s="0">
-        <v>220</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{5373313A-0822-4C8A-96F4-8E552924493A}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>